--- a/bao-cao-doanh-thu/doanh thu thông tin đơn hàng.xlsx
+++ b/bao-cao-doanh-thu/doanh thu thông tin đơn hàng.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="145">
   <si>
     <t xml:space="preserve">HƯỚNG DẪN SỬ DỤNG FILE BÁO CÁO DOANH THU - THÔNG TIN ĐƠN HÀNG (THÁNG 6 - THÁNG 12/2026)</t>
   </si>
@@ -45,7 +45,7 @@
     <t xml:space="preserve">2. CÁCH NHẬP LIỆU (trong các sheet tháng)</t>
   </si>
   <si>
-    <t xml:space="preserve">   • Chỉ nhập vào các cột: NGÀY ĐẶT, TÊN KHÁCH HÀNG, CÔNG TY, MÃ SỐ THUẾ, SỐ ĐIỆN THOẠI, TÊN SẢN PHẨM, SỐ LƯỢNG, ĐƠN GIÁ, HÌNH ẢNH, TÌNH TRẠNG CHUYỂN KHOẢN, GHI CHÚ.</t>
+    <t xml:space="preserve">   • Chỉ nhập vào các cột: NGÀY ĐẶT, TÊN KHÁCH HÀNG, CÔNG TY, MÃ SỐ THUẾ, SỐ ĐIỆN THOẠI, TÊN SẢN PHẨM, SỐ LƯỢNG, ĐƠN GIÁ, HÌNH ẢNH, TÌNH TRẠNG CHUYỂN KHOẢN, ĐỊA CHỈ GIAO HÀNG, GHI CHÚ.</t>
   </si>
   <si>
     <t xml:space="preserve">   • Cột STT và THÀNH TIỀN tự tính, KHÔNG sửa (Thành tiền = Số lượng × Đơn giá).</t>
@@ -75,7 +75,10 @@
     <t xml:space="preserve">4. BẢNG DOANH THU THEO NGÀY (bên phải mỗi sheet tháng)</t>
   </si>
   <si>
-    <t xml:space="preserve">   • Cột O-P của mỗi sheet tháng tự cộng doanh thu của từng ngày trong tháng đó.</t>
+    <t xml:space="preserve">   • Cột P-Q của mỗi sheet tháng tự cộng doanh thu của từng ngày trong tháng đó.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • File 'thông tin khách hàng đặt hàng' (file riêng) tự kéo NGÀY ĐẶT - TÊN - SĐT - ĐỊA CHỈ từ file này sang, không cần nhập lại.</t>
   </si>
   <si>
     <t xml:space="preserve">5. SHEET 'BÁO CÁO NĂM'</t>
@@ -159,6 +162,9 @@
     <t xml:space="preserve">TÌNH TRẠNG CHUYỂN KHOẢN</t>
   </si>
   <si>
+    <t xml:space="preserve">ĐỊA CHỈ GIAO HÀNG</t>
+  </si>
+  <si>
     <t xml:space="preserve">GHI CHÚ</t>
   </si>
   <si>
@@ -189,6 +195,9 @@
     <t xml:space="preserve">Đã chuyển khoản</t>
   </si>
   <si>
+    <t xml:space="preserve">12 Nguyễn Trãi, Thanh Xuân, Hà Nội</t>
+  </si>
+  <si>
     <t xml:space="preserve">Giao đợt 1 (VÍ DỤ MẪU)</t>
   </si>
   <si>
@@ -210,6 +219,9 @@
     <t xml:space="preserve">Chưa chuyển khoản</t>
   </si>
   <si>
+    <t xml:space="preserve">45 Lê Lợi, Quận 1, TP.HCM</t>
+  </si>
+  <si>
     <t xml:space="preserve">(VÍ DỤ MẪU)</t>
   </si>
   <si>
@@ -228,6 +240,9 @@
     <t xml:space="preserve">Bút ký khắc tên</t>
   </si>
   <si>
+    <t xml:space="preserve">88 Trần Phú, Hải Châu, Đà Nẵng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Khách quen (VÍ DỤ MẪU)</t>
   </si>
   <si>
@@ -235,6 +250,33 @@
   </si>
   <si>
     <t xml:space="preserve">BÁO CÁO DOANH THU THÁNG 7/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cty flc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ctyflc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2500740944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0866688324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tedy 25cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khách cũ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flc 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nvk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tedty 30</t>
   </si>
   <si>
     <t xml:space="preserve">BÁO CÁO DOANH THU THÁNG 8/2026</t>
@@ -996,7 +1038,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B34"/>
+  <dimension ref="B2:B35"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1093,15 +1135,15 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1116,39 +1158,44 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1167,7 +1214,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P407"/>
+  <dimension ref="A1:Q407"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="5"/>
@@ -1181,15 +1228,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="9" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1203,10 +1251,11 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -1216,7 +1265,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -1226,7 +1275,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
@@ -1235,56 +1284,59 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O6" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" s="14" t="s">
         <v>44</v>
       </c>
+      <c r="N7" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="P7" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1296,19 +1348,19 @@
         <v>46176</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H8" s="16" t="n">
         <v>100</v>
@@ -1321,19 +1373,22 @@
         <v>8500000</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="O8" s="18" t="n">
+        <v>55</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="P8" s="18" t="n">
         <v>46174</v>
       </c>
-      <c r="P8" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O8,$J$8:$J$407)</f>
+      <c r="Q8" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P8,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1346,19 +1401,19 @@
         <v>46183</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H9" s="16" t="n">
         <v>50</v>
@@ -1371,19 +1426,22 @@
         <v>6000000</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="O9" s="18" t="n">
+        <v>63</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="P9" s="18" t="n">
         <v>46175</v>
       </c>
-      <c r="P9" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O9,$J$8:$J$407)</f>
+      <c r="Q9" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P9,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1396,19 +1454,19 @@
         <v>46188</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H10" s="16" t="n">
         <v>200</v>
@@ -1421,19 +1479,22 @@
         <v>7000000</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="O10" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="P10" s="18" t="n">
         <v>46176</v>
       </c>
-      <c r="P10" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O10,$J$8:$J$407)</f>
+      <c r="Q10" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P10,$J$8:$J$407)</f>
         <v>8500000</v>
       </c>
     </row>
@@ -1446,11 +1507,11 @@
         <f aca="false">IF($H11="","",$H11*$I11)</f>
         <v/>
       </c>
-      <c r="O11" s="18" t="n">
+      <c r="P11" s="18" t="n">
         <v>46177</v>
       </c>
-      <c r="P11" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O11,$J$8:$J$407)</f>
+      <c r="Q11" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P11,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1463,11 +1524,11 @@
         <f aca="false">IF($H12="","",$H12*$I12)</f>
         <v/>
       </c>
-      <c r="O12" s="18" t="n">
+      <c r="P12" s="18" t="n">
         <v>46178</v>
       </c>
-      <c r="P12" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O12,$J$8:$J$407)</f>
+      <c r="Q12" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P12,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1480,11 +1541,11 @@
         <f aca="false">IF($H13="","",$H13*$I13)</f>
         <v/>
       </c>
-      <c r="O13" s="18" t="n">
+      <c r="P13" s="18" t="n">
         <v>46179</v>
       </c>
-      <c r="P13" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O13,$J$8:$J$407)</f>
+      <c r="Q13" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P13,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1497,11 +1558,11 @@
         <f aca="false">IF($H14="","",$H14*$I14)</f>
         <v/>
       </c>
-      <c r="O14" s="18" t="n">
+      <c r="P14" s="18" t="n">
         <v>46180</v>
       </c>
-      <c r="P14" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O14,$J$8:$J$407)</f>
+      <c r="Q14" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P14,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1514,11 +1575,11 @@
         <f aca="false">IF($H15="","",$H15*$I15)</f>
         <v/>
       </c>
-      <c r="O15" s="18" t="n">
+      <c r="P15" s="18" t="n">
         <v>46181</v>
       </c>
-      <c r="P15" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O15,$J$8:$J$407)</f>
+      <c r="Q15" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P15,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1531,11 +1592,11 @@
         <f aca="false">IF($H16="","",$H16*$I16)</f>
         <v/>
       </c>
-      <c r="O16" s="18" t="n">
+      <c r="P16" s="18" t="n">
         <v>46182</v>
       </c>
-      <c r="P16" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O16,$J$8:$J$407)</f>
+      <c r="Q16" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P16,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1548,11 +1609,11 @@
         <f aca="false">IF($H17="","",$H17*$I17)</f>
         <v/>
       </c>
-      <c r="O17" s="18" t="n">
+      <c r="P17" s="18" t="n">
         <v>46183</v>
       </c>
-      <c r="P17" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O17,$J$8:$J$407)</f>
+      <c r="Q17" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P17,$J$8:$J$407)</f>
         <v>6000000</v>
       </c>
     </row>
@@ -1565,11 +1626,11 @@
         <f aca="false">IF($H18="","",$H18*$I18)</f>
         <v/>
       </c>
-      <c r="O18" s="18" t="n">
+      <c r="P18" s="18" t="n">
         <v>46184</v>
       </c>
-      <c r="P18" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O18,$J$8:$J$407)</f>
+      <c r="Q18" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P18,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1582,11 +1643,11 @@
         <f aca="false">IF($H19="","",$H19*$I19)</f>
         <v/>
       </c>
-      <c r="O19" s="18" t="n">
+      <c r="P19" s="18" t="n">
         <v>46185</v>
       </c>
-      <c r="P19" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O19,$J$8:$J$407)</f>
+      <c r="Q19" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P19,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1599,11 +1660,11 @@
         <f aca="false">IF($H20="","",$H20*$I20)</f>
         <v/>
       </c>
-      <c r="O20" s="18" t="n">
+      <c r="P20" s="18" t="n">
         <v>46186</v>
       </c>
-      <c r="P20" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O20,$J$8:$J$407)</f>
+      <c r="Q20" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P20,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1616,11 +1677,11 @@
         <f aca="false">IF($H21="","",$H21*$I21)</f>
         <v/>
       </c>
-      <c r="O21" s="18" t="n">
+      <c r="P21" s="18" t="n">
         <v>46187</v>
       </c>
-      <c r="P21" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O21,$J$8:$J$407)</f>
+      <c r="Q21" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P21,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1633,11 +1694,11 @@
         <f aca="false">IF($H22="","",$H22*$I22)</f>
         <v/>
       </c>
-      <c r="O22" s="18" t="n">
+      <c r="P22" s="18" t="n">
         <v>46188</v>
       </c>
-      <c r="P22" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O22,$J$8:$J$407)</f>
+      <c r="Q22" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P22,$J$8:$J$407)</f>
         <v>7000000</v>
       </c>
     </row>
@@ -1650,11 +1711,11 @@
         <f aca="false">IF($H23="","",$H23*$I23)</f>
         <v/>
       </c>
-      <c r="O23" s="18" t="n">
+      <c r="P23" s="18" t="n">
         <v>46189</v>
       </c>
-      <c r="P23" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O23,$J$8:$J$407)</f>
+      <c r="Q23" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P23,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1667,11 +1728,11 @@
         <f aca="false">IF($H24="","",$H24*$I24)</f>
         <v/>
       </c>
-      <c r="O24" s="18" t="n">
+      <c r="P24" s="18" t="n">
         <v>46190</v>
       </c>
-      <c r="P24" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O24,$J$8:$J$407)</f>
+      <c r="Q24" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P24,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1684,11 +1745,11 @@
         <f aca="false">IF($H25="","",$H25*$I25)</f>
         <v/>
       </c>
-      <c r="O25" s="18" t="n">
+      <c r="P25" s="18" t="n">
         <v>46191</v>
       </c>
-      <c r="P25" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O25,$J$8:$J$407)</f>
+      <c r="Q25" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P25,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1701,11 +1762,11 @@
         <f aca="false">IF($H26="","",$H26*$I26)</f>
         <v/>
       </c>
-      <c r="O26" s="18" t="n">
+      <c r="P26" s="18" t="n">
         <v>46192</v>
       </c>
-      <c r="P26" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O26,$J$8:$J$407)</f>
+      <c r="Q26" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P26,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1718,11 +1779,11 @@
         <f aca="false">IF($H27="","",$H27*$I27)</f>
         <v/>
       </c>
-      <c r="O27" s="18" t="n">
+      <c r="P27" s="18" t="n">
         <v>46193</v>
       </c>
-      <c r="P27" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O27,$J$8:$J$407)</f>
+      <c r="Q27" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P27,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1735,11 +1796,11 @@
         <f aca="false">IF($H28="","",$H28*$I28)</f>
         <v/>
       </c>
-      <c r="O28" s="18" t="n">
+      <c r="P28" s="18" t="n">
         <v>46194</v>
       </c>
-      <c r="P28" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O28,$J$8:$J$407)</f>
+      <c r="Q28" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P28,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1752,11 +1813,11 @@
         <f aca="false">IF($H29="","",$H29*$I29)</f>
         <v/>
       </c>
-      <c r="O29" s="18" t="n">
+      <c r="P29" s="18" t="n">
         <v>46195</v>
       </c>
-      <c r="P29" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O29,$J$8:$J$407)</f>
+      <c r="Q29" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P29,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1769,11 +1830,11 @@
         <f aca="false">IF($H30="","",$H30*$I30)</f>
         <v/>
       </c>
-      <c r="O30" s="18" t="n">
+      <c r="P30" s="18" t="n">
         <v>46196</v>
       </c>
-      <c r="P30" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O30,$J$8:$J$407)</f>
+      <c r="Q30" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P30,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1786,11 +1847,11 @@
         <f aca="false">IF($H31="","",$H31*$I31)</f>
         <v/>
       </c>
-      <c r="O31" s="18" t="n">
+      <c r="P31" s="18" t="n">
         <v>46197</v>
       </c>
-      <c r="P31" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O31,$J$8:$J$407)</f>
+      <c r="Q31" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P31,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1803,11 +1864,11 @@
         <f aca="false">IF($H32="","",$H32*$I32)</f>
         <v/>
       </c>
-      <c r="O32" s="18" t="n">
+      <c r="P32" s="18" t="n">
         <v>46198</v>
       </c>
-      <c r="P32" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O32,$J$8:$J$407)</f>
+      <c r="Q32" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P32,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1820,11 +1881,11 @@
         <f aca="false">IF($H33="","",$H33*$I33)</f>
         <v/>
       </c>
-      <c r="O33" s="18" t="n">
+      <c r="P33" s="18" t="n">
         <v>46199</v>
       </c>
-      <c r="P33" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O33,$J$8:$J$407)</f>
+      <c r="Q33" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P33,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1837,11 +1898,11 @@
         <f aca="false">IF($H34="","",$H34*$I34)</f>
         <v/>
       </c>
-      <c r="O34" s="18" t="n">
+      <c r="P34" s="18" t="n">
         <v>46200</v>
       </c>
-      <c r="P34" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O34,$J$8:$J$407)</f>
+      <c r="Q34" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P34,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1854,11 +1915,11 @@
         <f aca="false">IF($H35="","",$H35*$I35)</f>
         <v/>
       </c>
-      <c r="O35" s="18" t="n">
+      <c r="P35" s="18" t="n">
         <v>46201</v>
       </c>
-      <c r="P35" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O35,$J$8:$J$407)</f>
+      <c r="Q35" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P35,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1871,11 +1932,11 @@
         <f aca="false">IF($H36="","",$H36*$I36)</f>
         <v/>
       </c>
-      <c r="O36" s="18" t="n">
+      <c r="P36" s="18" t="n">
         <v>46202</v>
       </c>
-      <c r="P36" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O36,$J$8:$J$407)</f>
+      <c r="Q36" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P36,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1888,11 +1949,11 @@
         <f aca="false">IF($H37="","",$H37*$I37)</f>
         <v/>
       </c>
-      <c r="O37" s="18" t="n">
+      <c r="P37" s="18" t="n">
         <v>46203</v>
       </c>
-      <c r="P37" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O37,$J$8:$J$407)</f>
+      <c r="Q37" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P37,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -1905,11 +1966,11 @@
         <f aca="false">IF($H38="","",$H38*$I38)</f>
         <v/>
       </c>
-      <c r="O38" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P38" s="21" t="n">
-        <f aca="false">SUM($P$8:$P$37)</f>
+      <c r="P38" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q38" s="21" t="n">
+        <f aca="false">SUM($Q$8:$Q$37)</f>
         <v>21500000</v>
       </c>
     </row>
@@ -5605,11 +5666,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="P6:Q6"/>
   </mergeCells>
   <conditionalFormatting sqref="L8:L407">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -5640,7 +5701,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P407"/>
+  <dimension ref="A1:Q407"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="5"/>
@@ -5654,15 +5715,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="9" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5676,121 +5738,179 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
         <f aca="false">SUM($J$8:$J$407)</f>
-        <v>0</v>
+        <v>97000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
         <f aca="false">SUMIF($L$8:$L$407,"Đã chuyển khoản",$J$8:$J$407)</f>
-        <v>0</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
         <f aca="false">SUMIF($L$8:$L$407,"Chưa chuyển khoản",$J$8:$J$407)</f>
-        <v>0</v>
+        <v>47000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O6" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" s="14" t="s">
         <v>44</v>
       </c>
+      <c r="N7" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="P7" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="str">
+      <c r="A8" s="4" t="n">
         <f aca="false">IF($B8="","",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="J8" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J8" s="9" t="n">
         <f aca="false">IF($H8="","",$H8*$I8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="18" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="P8" s="18" t="n">
         <v>46204</v>
       </c>
-      <c r="P8" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O8,$J$8:$J$407)</f>
+      <c r="Q8" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P8,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="str">
+      <c r="A9" s="4" t="n">
         <f aca="false">IF($B9="","",ROW()-7)</f>
-        <v/>
-      </c>
-      <c r="J9" s="9" t="str">
+        <v>2</v>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>47000</v>
+      </c>
+      <c r="J9" s="9" t="n">
         <f aca="false">IF($H9="","",$H9*$I9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="18" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="P9" s="18" t="n">
         <v>46205</v>
       </c>
-      <c r="P9" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O9,$J$8:$J$407)</f>
+      <c r="Q9" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P9,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5803,11 +5923,11 @@
         <f aca="false">IF($H10="","",$H10*$I10)</f>
         <v/>
       </c>
-      <c r="O10" s="18" t="n">
+      <c r="P10" s="18" t="n">
         <v>46206</v>
       </c>
-      <c r="P10" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O10,$J$8:$J$407)</f>
+      <c r="Q10" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P10,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5820,11 +5940,11 @@
         <f aca="false">IF($H11="","",$H11*$I11)</f>
         <v/>
       </c>
-      <c r="O11" s="18" t="n">
+      <c r="P11" s="18" t="n">
         <v>46207</v>
       </c>
-      <c r="P11" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O11,$J$8:$J$407)</f>
+      <c r="Q11" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P11,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5837,11 +5957,11 @@
         <f aca="false">IF($H12="","",$H12*$I12)</f>
         <v/>
       </c>
-      <c r="O12" s="18" t="n">
+      <c r="P12" s="18" t="n">
         <v>46208</v>
       </c>
-      <c r="P12" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O12,$J$8:$J$407)</f>
+      <c r="Q12" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P12,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5854,11 +5974,11 @@
         <f aca="false">IF($H13="","",$H13*$I13)</f>
         <v/>
       </c>
-      <c r="O13" s="18" t="n">
+      <c r="P13" s="18" t="n">
         <v>46209</v>
       </c>
-      <c r="P13" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O13,$J$8:$J$407)</f>
+      <c r="Q13" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P13,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5871,11 +5991,11 @@
         <f aca="false">IF($H14="","",$H14*$I14)</f>
         <v/>
       </c>
-      <c r="O14" s="18" t="n">
+      <c r="P14" s="18" t="n">
         <v>46210</v>
       </c>
-      <c r="P14" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O14,$J$8:$J$407)</f>
+      <c r="Q14" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P14,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5888,11 +6008,11 @@
         <f aca="false">IF($H15="","",$H15*$I15)</f>
         <v/>
       </c>
-      <c r="O15" s="18" t="n">
+      <c r="P15" s="18" t="n">
         <v>46211</v>
       </c>
-      <c r="P15" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O15,$J$8:$J$407)</f>
+      <c r="Q15" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P15,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5905,11 +6025,11 @@
         <f aca="false">IF($H16="","",$H16*$I16)</f>
         <v/>
       </c>
-      <c r="O16" s="18" t="n">
+      <c r="P16" s="18" t="n">
         <v>46212</v>
       </c>
-      <c r="P16" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O16,$J$8:$J$407)</f>
+      <c r="Q16" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P16,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5922,11 +6042,11 @@
         <f aca="false">IF($H17="","",$H17*$I17)</f>
         <v/>
       </c>
-      <c r="O17" s="18" t="n">
+      <c r="P17" s="18" t="n">
         <v>46213</v>
       </c>
-      <c r="P17" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O17,$J$8:$J$407)</f>
+      <c r="Q17" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P17,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5939,11 +6059,11 @@
         <f aca="false">IF($H18="","",$H18*$I18)</f>
         <v/>
       </c>
-      <c r="O18" s="18" t="n">
+      <c r="P18" s="18" t="n">
         <v>46214</v>
       </c>
-      <c r="P18" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O18,$J$8:$J$407)</f>
+      <c r="Q18" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P18,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5956,11 +6076,11 @@
         <f aca="false">IF($H19="","",$H19*$I19)</f>
         <v/>
       </c>
-      <c r="O19" s="18" t="n">
+      <c r="P19" s="18" t="n">
         <v>46215</v>
       </c>
-      <c r="P19" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O19,$J$8:$J$407)</f>
+      <c r="Q19" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P19,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5973,11 +6093,11 @@
         <f aca="false">IF($H20="","",$H20*$I20)</f>
         <v/>
       </c>
-      <c r="O20" s="18" t="n">
+      <c r="P20" s="18" t="n">
         <v>46216</v>
       </c>
-      <c r="P20" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O20,$J$8:$J$407)</f>
+      <c r="Q20" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P20,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -5990,11 +6110,11 @@
         <f aca="false">IF($H21="","",$H21*$I21)</f>
         <v/>
       </c>
-      <c r="O21" s="18" t="n">
+      <c r="P21" s="18" t="n">
         <v>46217</v>
       </c>
-      <c r="P21" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O21,$J$8:$J$407)</f>
+      <c r="Q21" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P21,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6007,11 +6127,11 @@
         <f aca="false">IF($H22="","",$H22*$I22)</f>
         <v/>
       </c>
-      <c r="O22" s="18" t="n">
+      <c r="P22" s="18" t="n">
         <v>46218</v>
       </c>
-      <c r="P22" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O22,$J$8:$J$407)</f>
+      <c r="Q22" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P22,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6024,11 +6144,11 @@
         <f aca="false">IF($H23="","",$H23*$I23)</f>
         <v/>
       </c>
-      <c r="O23" s="18" t="n">
+      <c r="P23" s="18" t="n">
         <v>46219</v>
       </c>
-      <c r="P23" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O23,$J$8:$J$407)</f>
+      <c r="Q23" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P23,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6041,11 +6161,11 @@
         <f aca="false">IF($H24="","",$H24*$I24)</f>
         <v/>
       </c>
-      <c r="O24" s="18" t="n">
+      <c r="P24" s="18" t="n">
         <v>46220</v>
       </c>
-      <c r="P24" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O24,$J$8:$J$407)</f>
+      <c r="Q24" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P24,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6058,11 +6178,11 @@
         <f aca="false">IF($H25="","",$H25*$I25)</f>
         <v/>
       </c>
-      <c r="O25" s="18" t="n">
+      <c r="P25" s="18" t="n">
         <v>46221</v>
       </c>
-      <c r="P25" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O25,$J$8:$J$407)</f>
+      <c r="Q25" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P25,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6075,11 +6195,11 @@
         <f aca="false">IF($H26="","",$H26*$I26)</f>
         <v/>
       </c>
-      <c r="O26" s="18" t="n">
+      <c r="P26" s="18" t="n">
         <v>46222</v>
       </c>
-      <c r="P26" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O26,$J$8:$J$407)</f>
+      <c r="Q26" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P26,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6092,11 +6212,11 @@
         <f aca="false">IF($H27="","",$H27*$I27)</f>
         <v/>
       </c>
-      <c r="O27" s="18" t="n">
+      <c r="P27" s="18" t="n">
         <v>46223</v>
       </c>
-      <c r="P27" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O27,$J$8:$J$407)</f>
+      <c r="Q27" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P27,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6109,12 +6229,12 @@
         <f aca="false">IF($H28="","",$H28*$I28)</f>
         <v/>
       </c>
-      <c r="O28" s="18" t="n">
+      <c r="P28" s="18" t="n">
         <v>46224</v>
       </c>
-      <c r="P28" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O28,$J$8:$J$407)</f>
-        <v>0</v>
+      <c r="Q28" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P28,$J$8:$J$407)</f>
+        <v>97000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6126,11 +6246,11 @@
         <f aca="false">IF($H29="","",$H29*$I29)</f>
         <v/>
       </c>
-      <c r="O29" s="18" t="n">
+      <c r="P29" s="18" t="n">
         <v>46225</v>
       </c>
-      <c r="P29" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O29,$J$8:$J$407)</f>
+      <c r="Q29" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P29,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6143,11 +6263,11 @@
         <f aca="false">IF($H30="","",$H30*$I30)</f>
         <v/>
       </c>
-      <c r="O30" s="18" t="n">
+      <c r="P30" s="18" t="n">
         <v>46226</v>
       </c>
-      <c r="P30" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O30,$J$8:$J$407)</f>
+      <c r="Q30" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P30,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6160,11 +6280,11 @@
         <f aca="false">IF($H31="","",$H31*$I31)</f>
         <v/>
       </c>
-      <c r="O31" s="18" t="n">
+      <c r="P31" s="18" t="n">
         <v>46227</v>
       </c>
-      <c r="P31" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O31,$J$8:$J$407)</f>
+      <c r="Q31" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P31,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6177,11 +6297,11 @@
         <f aca="false">IF($H32="","",$H32*$I32)</f>
         <v/>
       </c>
-      <c r="O32" s="18" t="n">
+      <c r="P32" s="18" t="n">
         <v>46228</v>
       </c>
-      <c r="P32" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O32,$J$8:$J$407)</f>
+      <c r="Q32" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P32,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6194,11 +6314,11 @@
         <f aca="false">IF($H33="","",$H33*$I33)</f>
         <v/>
       </c>
-      <c r="O33" s="18" t="n">
+      <c r="P33" s="18" t="n">
         <v>46229</v>
       </c>
-      <c r="P33" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O33,$J$8:$J$407)</f>
+      <c r="Q33" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P33,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6211,11 +6331,11 @@
         <f aca="false">IF($H34="","",$H34*$I34)</f>
         <v/>
       </c>
-      <c r="O34" s="18" t="n">
+      <c r="P34" s="18" t="n">
         <v>46230</v>
       </c>
-      <c r="P34" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O34,$J$8:$J$407)</f>
+      <c r="Q34" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P34,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6228,11 +6348,11 @@
         <f aca="false">IF($H35="","",$H35*$I35)</f>
         <v/>
       </c>
-      <c r="O35" s="18" t="n">
+      <c r="P35" s="18" t="n">
         <v>46231</v>
       </c>
-      <c r="P35" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O35,$J$8:$J$407)</f>
+      <c r="Q35" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P35,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6245,11 +6365,11 @@
         <f aca="false">IF($H36="","",$H36*$I36)</f>
         <v/>
       </c>
-      <c r="O36" s="18" t="n">
+      <c r="P36" s="18" t="n">
         <v>46232</v>
       </c>
-      <c r="P36" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O36,$J$8:$J$407)</f>
+      <c r="Q36" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P36,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6262,11 +6382,11 @@
         <f aca="false">IF($H37="","",$H37*$I37)</f>
         <v/>
       </c>
-      <c r="O37" s="18" t="n">
+      <c r="P37" s="18" t="n">
         <v>46233</v>
       </c>
-      <c r="P37" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O37,$J$8:$J$407)</f>
+      <c r="Q37" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P37,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6279,11 +6399,11 @@
         <f aca="false">IF($H38="","",$H38*$I38)</f>
         <v/>
       </c>
-      <c r="O38" s="18" t="n">
+      <c r="P38" s="18" t="n">
         <v>46234</v>
       </c>
-      <c r="P38" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O38,$J$8:$J$407)</f>
+      <c r="Q38" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P38,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -6296,12 +6416,12 @@
         <f aca="false">IF($H39="","",$H39*$I39)</f>
         <v/>
       </c>
-      <c r="O39" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P39" s="21" t="n">
-        <f aca="false">SUM($P$8:$P$38)</f>
-        <v>0</v>
+      <c r="P39" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q39" s="21" t="n">
+        <f aca="false">SUM($Q$8:$Q$38)</f>
+        <v>97000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9986,11 +10106,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="P6:Q6"/>
   </mergeCells>
   <conditionalFormatting sqref="L8:L407">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -10021,7 +10141,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P407"/>
+  <dimension ref="A1:Q407"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="5"/>
@@ -10035,15 +10155,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="9" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10057,10 +10178,11 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -10070,7 +10192,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -10080,7 +10202,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
@@ -10089,56 +10211,59 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O6" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" s="14" t="s">
         <v>44</v>
       </c>
+      <c r="N7" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="P7" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10150,11 +10275,11 @@
         <f aca="false">IF($H8="","",$H8*$I8)</f>
         <v/>
       </c>
-      <c r="O8" s="18" t="n">
+      <c r="P8" s="18" t="n">
         <v>46235</v>
       </c>
-      <c r="P8" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O8,$J$8:$J$407)</f>
+      <c r="Q8" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P8,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10167,11 +10292,11 @@
         <f aca="false">IF($H9="","",$H9*$I9)</f>
         <v/>
       </c>
-      <c r="O9" s="18" t="n">
+      <c r="P9" s="18" t="n">
         <v>46236</v>
       </c>
-      <c r="P9" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O9,$J$8:$J$407)</f>
+      <c r="Q9" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P9,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10184,11 +10309,11 @@
         <f aca="false">IF($H10="","",$H10*$I10)</f>
         <v/>
       </c>
-      <c r="O10" s="18" t="n">
+      <c r="P10" s="18" t="n">
         <v>46237</v>
       </c>
-      <c r="P10" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O10,$J$8:$J$407)</f>
+      <c r="Q10" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P10,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10201,11 +10326,11 @@
         <f aca="false">IF($H11="","",$H11*$I11)</f>
         <v/>
       </c>
-      <c r="O11" s="18" t="n">
+      <c r="P11" s="18" t="n">
         <v>46238</v>
       </c>
-      <c r="P11" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O11,$J$8:$J$407)</f>
+      <c r="Q11" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P11,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10218,11 +10343,11 @@
         <f aca="false">IF($H12="","",$H12*$I12)</f>
         <v/>
       </c>
-      <c r="O12" s="18" t="n">
+      <c r="P12" s="18" t="n">
         <v>46239</v>
       </c>
-      <c r="P12" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O12,$J$8:$J$407)</f>
+      <c r="Q12" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P12,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10235,11 +10360,11 @@
         <f aca="false">IF($H13="","",$H13*$I13)</f>
         <v/>
       </c>
-      <c r="O13" s="18" t="n">
+      <c r="P13" s="18" t="n">
         <v>46240</v>
       </c>
-      <c r="P13" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O13,$J$8:$J$407)</f>
+      <c r="Q13" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P13,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10252,11 +10377,11 @@
         <f aca="false">IF($H14="","",$H14*$I14)</f>
         <v/>
       </c>
-      <c r="O14" s="18" t="n">
+      <c r="P14" s="18" t="n">
         <v>46241</v>
       </c>
-      <c r="P14" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O14,$J$8:$J$407)</f>
+      <c r="Q14" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P14,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10269,11 +10394,11 @@
         <f aca="false">IF($H15="","",$H15*$I15)</f>
         <v/>
       </c>
-      <c r="O15" s="18" t="n">
+      <c r="P15" s="18" t="n">
         <v>46242</v>
       </c>
-      <c r="P15" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O15,$J$8:$J$407)</f>
+      <c r="Q15" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P15,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10286,11 +10411,11 @@
         <f aca="false">IF($H16="","",$H16*$I16)</f>
         <v/>
       </c>
-      <c r="O16" s="18" t="n">
+      <c r="P16" s="18" t="n">
         <v>46243</v>
       </c>
-      <c r="P16" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O16,$J$8:$J$407)</f>
+      <c r="Q16" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P16,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10303,11 +10428,11 @@
         <f aca="false">IF($H17="","",$H17*$I17)</f>
         <v/>
       </c>
-      <c r="O17" s="18" t="n">
+      <c r="P17" s="18" t="n">
         <v>46244</v>
       </c>
-      <c r="P17" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O17,$J$8:$J$407)</f>
+      <c r="Q17" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P17,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10320,11 +10445,11 @@
         <f aca="false">IF($H18="","",$H18*$I18)</f>
         <v/>
       </c>
-      <c r="O18" s="18" t="n">
+      <c r="P18" s="18" t="n">
         <v>46245</v>
       </c>
-      <c r="P18" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O18,$J$8:$J$407)</f>
+      <c r="Q18" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P18,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10337,11 +10462,11 @@
         <f aca="false">IF($H19="","",$H19*$I19)</f>
         <v/>
       </c>
-      <c r="O19" s="18" t="n">
+      <c r="P19" s="18" t="n">
         <v>46246</v>
       </c>
-      <c r="P19" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O19,$J$8:$J$407)</f>
+      <c r="Q19" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P19,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10354,11 +10479,11 @@
         <f aca="false">IF($H20="","",$H20*$I20)</f>
         <v/>
       </c>
-      <c r="O20" s="18" t="n">
+      <c r="P20" s="18" t="n">
         <v>46247</v>
       </c>
-      <c r="P20" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O20,$J$8:$J$407)</f>
+      <c r="Q20" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P20,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10371,11 +10496,11 @@
         <f aca="false">IF($H21="","",$H21*$I21)</f>
         <v/>
       </c>
-      <c r="O21" s="18" t="n">
+      <c r="P21" s="18" t="n">
         <v>46248</v>
       </c>
-      <c r="P21" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O21,$J$8:$J$407)</f>
+      <c r="Q21" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P21,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10388,11 +10513,11 @@
         <f aca="false">IF($H22="","",$H22*$I22)</f>
         <v/>
       </c>
-      <c r="O22" s="18" t="n">
+      <c r="P22" s="18" t="n">
         <v>46249</v>
       </c>
-      <c r="P22" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O22,$J$8:$J$407)</f>
+      <c r="Q22" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P22,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10405,11 +10530,11 @@
         <f aca="false">IF($H23="","",$H23*$I23)</f>
         <v/>
       </c>
-      <c r="O23" s="18" t="n">
+      <c r="P23" s="18" t="n">
         <v>46250</v>
       </c>
-      <c r="P23" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O23,$J$8:$J$407)</f>
+      <c r="Q23" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P23,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10422,11 +10547,11 @@
         <f aca="false">IF($H24="","",$H24*$I24)</f>
         <v/>
       </c>
-      <c r="O24" s="18" t="n">
+      <c r="P24" s="18" t="n">
         <v>46251</v>
       </c>
-      <c r="P24" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O24,$J$8:$J$407)</f>
+      <c r="Q24" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P24,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10439,11 +10564,11 @@
         <f aca="false">IF($H25="","",$H25*$I25)</f>
         <v/>
       </c>
-      <c r="O25" s="18" t="n">
+      <c r="P25" s="18" t="n">
         <v>46252</v>
       </c>
-      <c r="P25" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O25,$J$8:$J$407)</f>
+      <c r="Q25" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P25,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10456,11 +10581,11 @@
         <f aca="false">IF($H26="","",$H26*$I26)</f>
         <v/>
       </c>
-      <c r="O26" s="18" t="n">
+      <c r="P26" s="18" t="n">
         <v>46253</v>
       </c>
-      <c r="P26" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O26,$J$8:$J$407)</f>
+      <c r="Q26" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P26,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10473,11 +10598,11 @@
         <f aca="false">IF($H27="","",$H27*$I27)</f>
         <v/>
       </c>
-      <c r="O27" s="18" t="n">
+      <c r="P27" s="18" t="n">
         <v>46254</v>
       </c>
-      <c r="P27" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O27,$J$8:$J$407)</f>
+      <c r="Q27" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P27,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10490,11 +10615,11 @@
         <f aca="false">IF($H28="","",$H28*$I28)</f>
         <v/>
       </c>
-      <c r="O28" s="18" t="n">
+      <c r="P28" s="18" t="n">
         <v>46255</v>
       </c>
-      <c r="P28" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O28,$J$8:$J$407)</f>
+      <c r="Q28" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P28,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10507,11 +10632,11 @@
         <f aca="false">IF($H29="","",$H29*$I29)</f>
         <v/>
       </c>
-      <c r="O29" s="18" t="n">
+      <c r="P29" s="18" t="n">
         <v>46256</v>
       </c>
-      <c r="P29" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O29,$J$8:$J$407)</f>
+      <c r="Q29" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P29,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10524,11 +10649,11 @@
         <f aca="false">IF($H30="","",$H30*$I30)</f>
         <v/>
       </c>
-      <c r="O30" s="18" t="n">
+      <c r="P30" s="18" t="n">
         <v>46257</v>
       </c>
-      <c r="P30" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O30,$J$8:$J$407)</f>
+      <c r="Q30" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P30,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10541,11 +10666,11 @@
         <f aca="false">IF($H31="","",$H31*$I31)</f>
         <v/>
       </c>
-      <c r="O31" s="18" t="n">
+      <c r="P31" s="18" t="n">
         <v>46258</v>
       </c>
-      <c r="P31" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O31,$J$8:$J$407)</f>
+      <c r="Q31" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P31,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10558,11 +10683,11 @@
         <f aca="false">IF($H32="","",$H32*$I32)</f>
         <v/>
       </c>
-      <c r="O32" s="18" t="n">
+      <c r="P32" s="18" t="n">
         <v>46259</v>
       </c>
-      <c r="P32" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O32,$J$8:$J$407)</f>
+      <c r="Q32" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P32,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10575,11 +10700,11 @@
         <f aca="false">IF($H33="","",$H33*$I33)</f>
         <v/>
       </c>
-      <c r="O33" s="18" t="n">
+      <c r="P33" s="18" t="n">
         <v>46260</v>
       </c>
-      <c r="P33" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O33,$J$8:$J$407)</f>
+      <c r="Q33" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P33,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10592,11 +10717,11 @@
         <f aca="false">IF($H34="","",$H34*$I34)</f>
         <v/>
       </c>
-      <c r="O34" s="18" t="n">
+      <c r="P34" s="18" t="n">
         <v>46261</v>
       </c>
-      <c r="P34" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O34,$J$8:$J$407)</f>
+      <c r="Q34" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P34,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10609,11 +10734,11 @@
         <f aca="false">IF($H35="","",$H35*$I35)</f>
         <v/>
       </c>
-      <c r="O35" s="18" t="n">
+      <c r="P35" s="18" t="n">
         <v>46262</v>
       </c>
-      <c r="P35" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O35,$J$8:$J$407)</f>
+      <c r="Q35" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P35,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10626,11 +10751,11 @@
         <f aca="false">IF($H36="","",$H36*$I36)</f>
         <v/>
       </c>
-      <c r="O36" s="18" t="n">
+      <c r="P36" s="18" t="n">
         <v>46263</v>
       </c>
-      <c r="P36" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O36,$J$8:$J$407)</f>
+      <c r="Q36" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P36,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10643,11 +10768,11 @@
         <f aca="false">IF($H37="","",$H37*$I37)</f>
         <v/>
       </c>
-      <c r="O37" s="18" t="n">
+      <c r="P37" s="18" t="n">
         <v>46264</v>
       </c>
-      <c r="P37" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O37,$J$8:$J$407)</f>
+      <c r="Q37" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P37,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10660,11 +10785,11 @@
         <f aca="false">IF($H38="","",$H38*$I38)</f>
         <v/>
       </c>
-      <c r="O38" s="18" t="n">
+      <c r="P38" s="18" t="n">
         <v>46265</v>
       </c>
-      <c r="P38" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O38,$J$8:$J$407)</f>
+      <c r="Q38" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P38,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -10677,11 +10802,11 @@
         <f aca="false">IF($H39="","",$H39*$I39)</f>
         <v/>
       </c>
-      <c r="O39" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P39" s="21" t="n">
-        <f aca="false">SUM($P$8:$P$38)</f>
+      <c r="P39" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q39" s="21" t="n">
+        <f aca="false">SUM($Q$8:$Q$38)</f>
         <v>0</v>
       </c>
     </row>
@@ -14367,11 +14492,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="P6:Q6"/>
   </mergeCells>
   <conditionalFormatting sqref="L8:L407">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -14402,7 +14527,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P407"/>
+  <dimension ref="A1:Q407"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="5"/>
@@ -14416,15 +14541,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="9" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -14438,10 +14564,11 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -14451,7 +14578,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -14461,7 +14588,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
@@ -14470,56 +14597,59 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O6" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" s="14" t="s">
         <v>44</v>
       </c>
+      <c r="N7" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="P7" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14531,11 +14661,11 @@
         <f aca="false">IF($H8="","",$H8*$I8)</f>
         <v/>
       </c>
-      <c r="O8" s="18" t="n">
+      <c r="P8" s="18" t="n">
         <v>46266</v>
       </c>
-      <c r="P8" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O8,$J$8:$J$407)</f>
+      <c r="Q8" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P8,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14548,11 +14678,11 @@
         <f aca="false">IF($H9="","",$H9*$I9)</f>
         <v/>
       </c>
-      <c r="O9" s="18" t="n">
+      <c r="P9" s="18" t="n">
         <v>46267</v>
       </c>
-      <c r="P9" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O9,$J$8:$J$407)</f>
+      <c r="Q9" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P9,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14565,11 +14695,11 @@
         <f aca="false">IF($H10="","",$H10*$I10)</f>
         <v/>
       </c>
-      <c r="O10" s="18" t="n">
+      <c r="P10" s="18" t="n">
         <v>46268</v>
       </c>
-      <c r="P10" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O10,$J$8:$J$407)</f>
+      <c r="Q10" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P10,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14582,11 +14712,11 @@
         <f aca="false">IF($H11="","",$H11*$I11)</f>
         <v/>
       </c>
-      <c r="O11" s="18" t="n">
+      <c r="P11" s="18" t="n">
         <v>46269</v>
       </c>
-      <c r="P11" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O11,$J$8:$J$407)</f>
+      <c r="Q11" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P11,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14599,11 +14729,11 @@
         <f aca="false">IF($H12="","",$H12*$I12)</f>
         <v/>
       </c>
-      <c r="O12" s="18" t="n">
+      <c r="P12" s="18" t="n">
         <v>46270</v>
       </c>
-      <c r="P12" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O12,$J$8:$J$407)</f>
+      <c r="Q12" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P12,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14616,11 +14746,11 @@
         <f aca="false">IF($H13="","",$H13*$I13)</f>
         <v/>
       </c>
-      <c r="O13" s="18" t="n">
+      <c r="P13" s="18" t="n">
         <v>46271</v>
       </c>
-      <c r="P13" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O13,$J$8:$J$407)</f>
+      <c r="Q13" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P13,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14633,11 +14763,11 @@
         <f aca="false">IF($H14="","",$H14*$I14)</f>
         <v/>
       </c>
-      <c r="O14" s="18" t="n">
+      <c r="P14" s="18" t="n">
         <v>46272</v>
       </c>
-      <c r="P14" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O14,$J$8:$J$407)</f>
+      <c r="Q14" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P14,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14650,11 +14780,11 @@
         <f aca="false">IF($H15="","",$H15*$I15)</f>
         <v/>
       </c>
-      <c r="O15" s="18" t="n">
+      <c r="P15" s="18" t="n">
         <v>46273</v>
       </c>
-      <c r="P15" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O15,$J$8:$J$407)</f>
+      <c r="Q15" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P15,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14667,11 +14797,11 @@
         <f aca="false">IF($H16="","",$H16*$I16)</f>
         <v/>
       </c>
-      <c r="O16" s="18" t="n">
+      <c r="P16" s="18" t="n">
         <v>46274</v>
       </c>
-      <c r="P16" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O16,$J$8:$J$407)</f>
+      <c r="Q16" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P16,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14684,11 +14814,11 @@
         <f aca="false">IF($H17="","",$H17*$I17)</f>
         <v/>
       </c>
-      <c r="O17" s="18" t="n">
+      <c r="P17" s="18" t="n">
         <v>46275</v>
       </c>
-      <c r="P17" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O17,$J$8:$J$407)</f>
+      <c r="Q17" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P17,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14701,11 +14831,11 @@
         <f aca="false">IF($H18="","",$H18*$I18)</f>
         <v/>
       </c>
-      <c r="O18" s="18" t="n">
+      <c r="P18" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="P18" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O18,$J$8:$J$407)</f>
+      <c r="Q18" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P18,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14718,11 +14848,11 @@
         <f aca="false">IF($H19="","",$H19*$I19)</f>
         <v/>
       </c>
-      <c r="O19" s="18" t="n">
+      <c r="P19" s="18" t="n">
         <v>46277</v>
       </c>
-      <c r="P19" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O19,$J$8:$J$407)</f>
+      <c r="Q19" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P19,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14735,11 +14865,11 @@
         <f aca="false">IF($H20="","",$H20*$I20)</f>
         <v/>
       </c>
-      <c r="O20" s="18" t="n">
+      <c r="P20" s="18" t="n">
         <v>46278</v>
       </c>
-      <c r="P20" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O20,$J$8:$J$407)</f>
+      <c r="Q20" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P20,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14752,11 +14882,11 @@
         <f aca="false">IF($H21="","",$H21*$I21)</f>
         <v/>
       </c>
-      <c r="O21" s="18" t="n">
+      <c r="P21" s="18" t="n">
         <v>46279</v>
       </c>
-      <c r="P21" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O21,$J$8:$J$407)</f>
+      <c r="Q21" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P21,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14769,11 +14899,11 @@
         <f aca="false">IF($H22="","",$H22*$I22)</f>
         <v/>
       </c>
-      <c r="O22" s="18" t="n">
+      <c r="P22" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="P22" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O22,$J$8:$J$407)</f>
+      <c r="Q22" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P22,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14786,11 +14916,11 @@
         <f aca="false">IF($H23="","",$H23*$I23)</f>
         <v/>
       </c>
-      <c r="O23" s="18" t="n">
+      <c r="P23" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="P23" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O23,$J$8:$J$407)</f>
+      <c r="Q23" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P23,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14803,11 +14933,11 @@
         <f aca="false">IF($H24="","",$H24*$I24)</f>
         <v/>
       </c>
-      <c r="O24" s="18" t="n">
+      <c r="P24" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="P24" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O24,$J$8:$J$407)</f>
+      <c r="Q24" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P24,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14820,11 +14950,11 @@
         <f aca="false">IF($H25="","",$H25*$I25)</f>
         <v/>
       </c>
-      <c r="O25" s="18" t="n">
+      <c r="P25" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="P25" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O25,$J$8:$J$407)</f>
+      <c r="Q25" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P25,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14837,11 +14967,11 @@
         <f aca="false">IF($H26="","",$H26*$I26)</f>
         <v/>
       </c>
-      <c r="O26" s="18" t="n">
+      <c r="P26" s="18" t="n">
         <v>46284</v>
       </c>
-      <c r="P26" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O26,$J$8:$J$407)</f>
+      <c r="Q26" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P26,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14854,11 +14984,11 @@
         <f aca="false">IF($H27="","",$H27*$I27)</f>
         <v/>
       </c>
-      <c r="O27" s="18" t="n">
+      <c r="P27" s="18" t="n">
         <v>46285</v>
       </c>
-      <c r="P27" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O27,$J$8:$J$407)</f>
+      <c r="Q27" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P27,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14871,11 +15001,11 @@
         <f aca="false">IF($H28="","",$H28*$I28)</f>
         <v/>
       </c>
-      <c r="O28" s="18" t="n">
+      <c r="P28" s="18" t="n">
         <v>46286</v>
       </c>
-      <c r="P28" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O28,$J$8:$J$407)</f>
+      <c r="Q28" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P28,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14888,11 +15018,11 @@
         <f aca="false">IF($H29="","",$H29*$I29)</f>
         <v/>
       </c>
-      <c r="O29" s="18" t="n">
+      <c r="P29" s="18" t="n">
         <v>46287</v>
       </c>
-      <c r="P29" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O29,$J$8:$J$407)</f>
+      <c r="Q29" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P29,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14905,11 +15035,11 @@
         <f aca="false">IF($H30="","",$H30*$I30)</f>
         <v/>
       </c>
-      <c r="O30" s="18" t="n">
+      <c r="P30" s="18" t="n">
         <v>46288</v>
       </c>
-      <c r="P30" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O30,$J$8:$J$407)</f>
+      <c r="Q30" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P30,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14922,11 +15052,11 @@
         <f aca="false">IF($H31="","",$H31*$I31)</f>
         <v/>
       </c>
-      <c r="O31" s="18" t="n">
+      <c r="P31" s="18" t="n">
         <v>46289</v>
       </c>
-      <c r="P31" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O31,$J$8:$J$407)</f>
+      <c r="Q31" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P31,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14939,11 +15069,11 @@
         <f aca="false">IF($H32="","",$H32*$I32)</f>
         <v/>
       </c>
-      <c r="O32" s="18" t="n">
+      <c r="P32" s="18" t="n">
         <v>46290</v>
       </c>
-      <c r="P32" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O32,$J$8:$J$407)</f>
+      <c r="Q32" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P32,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14956,11 +15086,11 @@
         <f aca="false">IF($H33="","",$H33*$I33)</f>
         <v/>
       </c>
-      <c r="O33" s="18" t="n">
+      <c r="P33" s="18" t="n">
         <v>46291</v>
       </c>
-      <c r="P33" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O33,$J$8:$J$407)</f>
+      <c r="Q33" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P33,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14973,11 +15103,11 @@
         <f aca="false">IF($H34="","",$H34*$I34)</f>
         <v/>
       </c>
-      <c r="O34" s="18" t="n">
+      <c r="P34" s="18" t="n">
         <v>46292</v>
       </c>
-      <c r="P34" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O34,$J$8:$J$407)</f>
+      <c r="Q34" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P34,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -14990,11 +15120,11 @@
         <f aca="false">IF($H35="","",$H35*$I35)</f>
         <v/>
       </c>
-      <c r="O35" s="18" t="n">
+      <c r="P35" s="18" t="n">
         <v>46293</v>
       </c>
-      <c r="P35" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O35,$J$8:$J$407)</f>
+      <c r="Q35" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P35,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -15007,11 +15137,11 @@
         <f aca="false">IF($H36="","",$H36*$I36)</f>
         <v/>
       </c>
-      <c r="O36" s="18" t="n">
+      <c r="P36" s="18" t="n">
         <v>46294</v>
       </c>
-      <c r="P36" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O36,$J$8:$J$407)</f>
+      <c r="Q36" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P36,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -15024,11 +15154,11 @@
         <f aca="false">IF($H37="","",$H37*$I37)</f>
         <v/>
       </c>
-      <c r="O37" s="18" t="n">
+      <c r="P37" s="18" t="n">
         <v>46295</v>
       </c>
-      <c r="P37" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O37,$J$8:$J$407)</f>
+      <c r="Q37" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P37,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -15041,11 +15171,11 @@
         <f aca="false">IF($H38="","",$H38*$I38)</f>
         <v/>
       </c>
-      <c r="O38" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P38" s="21" t="n">
-        <f aca="false">SUM($P$8:$P$37)</f>
+      <c r="P38" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q38" s="21" t="n">
+        <f aca="false">SUM($Q$8:$Q$37)</f>
         <v>0</v>
       </c>
     </row>
@@ -18741,11 +18871,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="P6:Q6"/>
   </mergeCells>
   <conditionalFormatting sqref="L8:L407">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -18776,7 +18906,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P407"/>
+  <dimension ref="A1:Q407"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="5"/>
@@ -18790,15 +18920,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="9" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -18812,10 +18943,11 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -18825,7 +18957,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -18835,7 +18967,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
@@ -18844,56 +18976,59 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O6" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" s="14" t="s">
         <v>44</v>
       </c>
+      <c r="N7" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="P7" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18905,11 +19040,11 @@
         <f aca="false">IF($H8="","",$H8*$I8)</f>
         <v/>
       </c>
-      <c r="O8" s="18" t="n">
+      <c r="P8" s="18" t="n">
         <v>46296</v>
       </c>
-      <c r="P8" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O8,$J$8:$J$407)</f>
+      <c r="Q8" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P8,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -18922,11 +19057,11 @@
         <f aca="false">IF($H9="","",$H9*$I9)</f>
         <v/>
       </c>
-      <c r="O9" s="18" t="n">
+      <c r="P9" s="18" t="n">
         <v>46297</v>
       </c>
-      <c r="P9" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O9,$J$8:$J$407)</f>
+      <c r="Q9" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P9,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -18939,11 +19074,11 @@
         <f aca="false">IF($H10="","",$H10*$I10)</f>
         <v/>
       </c>
-      <c r="O10" s="18" t="n">
+      <c r="P10" s="18" t="n">
         <v>46298</v>
       </c>
-      <c r="P10" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O10,$J$8:$J$407)</f>
+      <c r="Q10" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P10,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -18956,11 +19091,11 @@
         <f aca="false">IF($H11="","",$H11*$I11)</f>
         <v/>
       </c>
-      <c r="O11" s="18" t="n">
+      <c r="P11" s="18" t="n">
         <v>46299</v>
       </c>
-      <c r="P11" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O11,$J$8:$J$407)</f>
+      <c r="Q11" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P11,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -18973,11 +19108,11 @@
         <f aca="false">IF($H12="","",$H12*$I12)</f>
         <v/>
       </c>
-      <c r="O12" s="18" t="n">
+      <c r="P12" s="18" t="n">
         <v>46300</v>
       </c>
-      <c r="P12" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O12,$J$8:$J$407)</f>
+      <c r="Q12" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P12,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -18990,11 +19125,11 @@
         <f aca="false">IF($H13="","",$H13*$I13)</f>
         <v/>
       </c>
-      <c r="O13" s="18" t="n">
+      <c r="P13" s="18" t="n">
         <v>46301</v>
       </c>
-      <c r="P13" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O13,$J$8:$J$407)</f>
+      <c r="Q13" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P13,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19007,11 +19142,11 @@
         <f aca="false">IF($H14="","",$H14*$I14)</f>
         <v/>
       </c>
-      <c r="O14" s="18" t="n">
+      <c r="P14" s="18" t="n">
         <v>46302</v>
       </c>
-      <c r="P14" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O14,$J$8:$J$407)</f>
+      <c r="Q14" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P14,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19024,11 +19159,11 @@
         <f aca="false">IF($H15="","",$H15*$I15)</f>
         <v/>
       </c>
-      <c r="O15" s="18" t="n">
+      <c r="P15" s="18" t="n">
         <v>46303</v>
       </c>
-      <c r="P15" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O15,$J$8:$J$407)</f>
+      <c r="Q15" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P15,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19041,11 +19176,11 @@
         <f aca="false">IF($H16="","",$H16*$I16)</f>
         <v/>
       </c>
-      <c r="O16" s="18" t="n">
+      <c r="P16" s="18" t="n">
         <v>46304</v>
       </c>
-      <c r="P16" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O16,$J$8:$J$407)</f>
+      <c r="Q16" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P16,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19058,11 +19193,11 @@
         <f aca="false">IF($H17="","",$H17*$I17)</f>
         <v/>
       </c>
-      <c r="O17" s="18" t="n">
+      <c r="P17" s="18" t="n">
         <v>46305</v>
       </c>
-      <c r="P17" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O17,$J$8:$J$407)</f>
+      <c r="Q17" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P17,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19075,11 +19210,11 @@
         <f aca="false">IF($H18="","",$H18*$I18)</f>
         <v/>
       </c>
-      <c r="O18" s="18" t="n">
+      <c r="P18" s="18" t="n">
         <v>46306</v>
       </c>
-      <c r="P18" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O18,$J$8:$J$407)</f>
+      <c r="Q18" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P18,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19092,11 +19227,11 @@
         <f aca="false">IF($H19="","",$H19*$I19)</f>
         <v/>
       </c>
-      <c r="O19" s="18" t="n">
+      <c r="P19" s="18" t="n">
         <v>46307</v>
       </c>
-      <c r="P19" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O19,$J$8:$J$407)</f>
+      <c r="Q19" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P19,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19109,11 +19244,11 @@
         <f aca="false">IF($H20="","",$H20*$I20)</f>
         <v/>
       </c>
-      <c r="O20" s="18" t="n">
+      <c r="P20" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="P20" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O20,$J$8:$J$407)</f>
+      <c r="Q20" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P20,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19126,11 +19261,11 @@
         <f aca="false">IF($H21="","",$H21*$I21)</f>
         <v/>
       </c>
-      <c r="O21" s="18" t="n">
+      <c r="P21" s="18" t="n">
         <v>46309</v>
       </c>
-      <c r="P21" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O21,$J$8:$J$407)</f>
+      <c r="Q21" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P21,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19143,11 +19278,11 @@
         <f aca="false">IF($H22="","",$H22*$I22)</f>
         <v/>
       </c>
-      <c r="O22" s="18" t="n">
+      <c r="P22" s="18" t="n">
         <v>46310</v>
       </c>
-      <c r="P22" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O22,$J$8:$J$407)</f>
+      <c r="Q22" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P22,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19160,11 +19295,11 @@
         <f aca="false">IF($H23="","",$H23*$I23)</f>
         <v/>
       </c>
-      <c r="O23" s="18" t="n">
+      <c r="P23" s="18" t="n">
         <v>46311</v>
       </c>
-      <c r="P23" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O23,$J$8:$J$407)</f>
+      <c r="Q23" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P23,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19177,11 +19312,11 @@
         <f aca="false">IF($H24="","",$H24*$I24)</f>
         <v/>
       </c>
-      <c r="O24" s="18" t="n">
+      <c r="P24" s="18" t="n">
         <v>46312</v>
       </c>
-      <c r="P24" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O24,$J$8:$J$407)</f>
+      <c r="Q24" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P24,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19194,11 +19329,11 @@
         <f aca="false">IF($H25="","",$H25*$I25)</f>
         <v/>
       </c>
-      <c r="O25" s="18" t="n">
+      <c r="P25" s="18" t="n">
         <v>46313</v>
       </c>
-      <c r="P25" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O25,$J$8:$J$407)</f>
+      <c r="Q25" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P25,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19211,11 +19346,11 @@
         <f aca="false">IF($H26="","",$H26*$I26)</f>
         <v/>
       </c>
-      <c r="O26" s="18" t="n">
+      <c r="P26" s="18" t="n">
         <v>46314</v>
       </c>
-      <c r="P26" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O26,$J$8:$J$407)</f>
+      <c r="Q26" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P26,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19228,11 +19363,11 @@
         <f aca="false">IF($H27="","",$H27*$I27)</f>
         <v/>
       </c>
-      <c r="O27" s="18" t="n">
+      <c r="P27" s="18" t="n">
         <v>46315</v>
       </c>
-      <c r="P27" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O27,$J$8:$J$407)</f>
+      <c r="Q27" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P27,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19245,11 +19380,11 @@
         <f aca="false">IF($H28="","",$H28*$I28)</f>
         <v/>
       </c>
-      <c r="O28" s="18" t="n">
+      <c r="P28" s="18" t="n">
         <v>46316</v>
       </c>
-      <c r="P28" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O28,$J$8:$J$407)</f>
+      <c r="Q28" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P28,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19262,11 +19397,11 @@
         <f aca="false">IF($H29="","",$H29*$I29)</f>
         <v/>
       </c>
-      <c r="O29" s="18" t="n">
+      <c r="P29" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="P29" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O29,$J$8:$J$407)</f>
+      <c r="Q29" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P29,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19279,11 +19414,11 @@
         <f aca="false">IF($H30="","",$H30*$I30)</f>
         <v/>
       </c>
-      <c r="O30" s="18" t="n">
+      <c r="P30" s="18" t="n">
         <v>46318</v>
       </c>
-      <c r="P30" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O30,$J$8:$J$407)</f>
+      <c r="Q30" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P30,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19296,11 +19431,11 @@
         <f aca="false">IF($H31="","",$H31*$I31)</f>
         <v/>
       </c>
-      <c r="O31" s="18" t="n">
+      <c r="P31" s="18" t="n">
         <v>46319</v>
       </c>
-      <c r="P31" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O31,$J$8:$J$407)</f>
+      <c r="Q31" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P31,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19313,11 +19448,11 @@
         <f aca="false">IF($H32="","",$H32*$I32)</f>
         <v/>
       </c>
-      <c r="O32" s="18" t="n">
+      <c r="P32" s="18" t="n">
         <v>46320</v>
       </c>
-      <c r="P32" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O32,$J$8:$J$407)</f>
+      <c r="Q32" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P32,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19330,11 +19465,11 @@
         <f aca="false">IF($H33="","",$H33*$I33)</f>
         <v/>
       </c>
-      <c r="O33" s="18" t="n">
+      <c r="P33" s="18" t="n">
         <v>46321</v>
       </c>
-      <c r="P33" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O33,$J$8:$J$407)</f>
+      <c r="Q33" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P33,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19347,11 +19482,11 @@
         <f aca="false">IF($H34="","",$H34*$I34)</f>
         <v/>
       </c>
-      <c r="O34" s="18" t="n">
+      <c r="P34" s="18" t="n">
         <v>46322</v>
       </c>
-      <c r="P34" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O34,$J$8:$J$407)</f>
+      <c r="Q34" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P34,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19364,11 +19499,11 @@
         <f aca="false">IF($H35="","",$H35*$I35)</f>
         <v/>
       </c>
-      <c r="O35" s="18" t="n">
+      <c r="P35" s="18" t="n">
         <v>46323</v>
       </c>
-      <c r="P35" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O35,$J$8:$J$407)</f>
+      <c r="Q35" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P35,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19381,11 +19516,11 @@
         <f aca="false">IF($H36="","",$H36*$I36)</f>
         <v/>
       </c>
-      <c r="O36" s="18" t="n">
+      <c r="P36" s="18" t="n">
         <v>46324</v>
       </c>
-      <c r="P36" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O36,$J$8:$J$407)</f>
+      <c r="Q36" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P36,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19398,11 +19533,11 @@
         <f aca="false">IF($H37="","",$H37*$I37)</f>
         <v/>
       </c>
-      <c r="O37" s="18" t="n">
+      <c r="P37" s="18" t="n">
         <v>46325</v>
       </c>
-      <c r="P37" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O37,$J$8:$J$407)</f>
+      <c r="Q37" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P37,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19415,11 +19550,11 @@
         <f aca="false">IF($H38="","",$H38*$I38)</f>
         <v/>
       </c>
-      <c r="O38" s="18" t="n">
+      <c r="P38" s="18" t="n">
         <v>46326</v>
       </c>
-      <c r="P38" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O38,$J$8:$J$407)</f>
+      <c r="Q38" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P38,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -19432,11 +19567,11 @@
         <f aca="false">IF($H39="","",$H39*$I39)</f>
         <v/>
       </c>
-      <c r="O39" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P39" s="21" t="n">
-        <f aca="false">SUM($P$8:$P$38)</f>
+      <c r="P39" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q39" s="21" t="n">
+        <f aca="false">SUM($Q$8:$Q$38)</f>
         <v>0</v>
       </c>
     </row>
@@ -23122,11 +23257,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="P6:Q6"/>
   </mergeCells>
   <conditionalFormatting sqref="L8:L407">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -23157,7 +23292,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P407"/>
+  <dimension ref="A1:Q407"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="5"/>
@@ -23171,15 +23306,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="9" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -23193,10 +23329,11 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -23206,7 +23343,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -23216,7 +23353,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
@@ -23225,56 +23362,59 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O6" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" s="14" t="s">
         <v>44</v>
       </c>
+      <c r="N7" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="P7" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23286,11 +23426,11 @@
         <f aca="false">IF($H8="","",$H8*$I8)</f>
         <v/>
       </c>
-      <c r="O8" s="18" t="n">
+      <c r="P8" s="18" t="n">
         <v>46327</v>
       </c>
-      <c r="P8" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O8,$J$8:$J$407)</f>
+      <c r="Q8" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P8,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23303,11 +23443,11 @@
         <f aca="false">IF($H9="","",$H9*$I9)</f>
         <v/>
       </c>
-      <c r="O9" s="18" t="n">
+      <c r="P9" s="18" t="n">
         <v>46328</v>
       </c>
-      <c r="P9" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O9,$J$8:$J$407)</f>
+      <c r="Q9" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P9,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23320,11 +23460,11 @@
         <f aca="false">IF($H10="","",$H10*$I10)</f>
         <v/>
       </c>
-      <c r="O10" s="18" t="n">
+      <c r="P10" s="18" t="n">
         <v>46329</v>
       </c>
-      <c r="P10" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O10,$J$8:$J$407)</f>
+      <c r="Q10" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P10,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23337,11 +23477,11 @@
         <f aca="false">IF($H11="","",$H11*$I11)</f>
         <v/>
       </c>
-      <c r="O11" s="18" t="n">
+      <c r="P11" s="18" t="n">
         <v>46330</v>
       </c>
-      <c r="P11" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O11,$J$8:$J$407)</f>
+      <c r="Q11" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P11,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23354,11 +23494,11 @@
         <f aca="false">IF($H12="","",$H12*$I12)</f>
         <v/>
       </c>
-      <c r="O12" s="18" t="n">
+      <c r="P12" s="18" t="n">
         <v>46331</v>
       </c>
-      <c r="P12" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O12,$J$8:$J$407)</f>
+      <c r="Q12" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P12,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23371,11 +23511,11 @@
         <f aca="false">IF($H13="","",$H13*$I13)</f>
         <v/>
       </c>
-      <c r="O13" s="18" t="n">
+      <c r="P13" s="18" t="n">
         <v>46332</v>
       </c>
-      <c r="P13" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O13,$J$8:$J$407)</f>
+      <c r="Q13" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P13,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23388,11 +23528,11 @@
         <f aca="false">IF($H14="","",$H14*$I14)</f>
         <v/>
       </c>
-      <c r="O14" s="18" t="n">
+      <c r="P14" s="18" t="n">
         <v>46333</v>
       </c>
-      <c r="P14" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O14,$J$8:$J$407)</f>
+      <c r="Q14" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P14,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23405,11 +23545,11 @@
         <f aca="false">IF($H15="","",$H15*$I15)</f>
         <v/>
       </c>
-      <c r="O15" s="18" t="n">
+      <c r="P15" s="18" t="n">
         <v>46334</v>
       </c>
-      <c r="P15" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O15,$J$8:$J$407)</f>
+      <c r="Q15" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P15,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23422,11 +23562,11 @@
         <f aca="false">IF($H16="","",$H16*$I16)</f>
         <v/>
       </c>
-      <c r="O16" s="18" t="n">
+      <c r="P16" s="18" t="n">
         <v>46335</v>
       </c>
-      <c r="P16" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O16,$J$8:$J$407)</f>
+      <c r="Q16" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P16,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23439,11 +23579,11 @@
         <f aca="false">IF($H17="","",$H17*$I17)</f>
         <v/>
       </c>
-      <c r="O17" s="18" t="n">
+      <c r="P17" s="18" t="n">
         <v>46336</v>
       </c>
-      <c r="P17" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O17,$J$8:$J$407)</f>
+      <c r="Q17" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P17,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23456,11 +23596,11 @@
         <f aca="false">IF($H18="","",$H18*$I18)</f>
         <v/>
       </c>
-      <c r="O18" s="18" t="n">
+      <c r="P18" s="18" t="n">
         <v>46337</v>
       </c>
-      <c r="P18" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O18,$J$8:$J$407)</f>
+      <c r="Q18" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P18,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23473,11 +23613,11 @@
         <f aca="false">IF($H19="","",$H19*$I19)</f>
         <v/>
       </c>
-      <c r="O19" s="18" t="n">
+      <c r="P19" s="18" t="n">
         <v>46338</v>
       </c>
-      <c r="P19" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O19,$J$8:$J$407)</f>
+      <c r="Q19" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P19,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23490,11 +23630,11 @@
         <f aca="false">IF($H20="","",$H20*$I20)</f>
         <v/>
       </c>
-      <c r="O20" s="18" t="n">
+      <c r="P20" s="18" t="n">
         <v>46339</v>
       </c>
-      <c r="P20" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O20,$J$8:$J$407)</f>
+      <c r="Q20" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P20,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23507,11 +23647,11 @@
         <f aca="false">IF($H21="","",$H21*$I21)</f>
         <v/>
       </c>
-      <c r="O21" s="18" t="n">
+      <c r="P21" s="18" t="n">
         <v>46340</v>
       </c>
-      <c r="P21" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O21,$J$8:$J$407)</f>
+      <c r="Q21" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P21,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23524,11 +23664,11 @@
         <f aca="false">IF($H22="","",$H22*$I22)</f>
         <v/>
       </c>
-      <c r="O22" s="18" t="n">
+      <c r="P22" s="18" t="n">
         <v>46341</v>
       </c>
-      <c r="P22" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O22,$J$8:$J$407)</f>
+      <c r="Q22" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P22,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23541,11 +23681,11 @@
         <f aca="false">IF($H23="","",$H23*$I23)</f>
         <v/>
       </c>
-      <c r="O23" s="18" t="n">
+      <c r="P23" s="18" t="n">
         <v>46342</v>
       </c>
-      <c r="P23" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O23,$J$8:$J$407)</f>
+      <c r="Q23" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P23,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23558,11 +23698,11 @@
         <f aca="false">IF($H24="","",$H24*$I24)</f>
         <v/>
       </c>
-      <c r="O24" s="18" t="n">
+      <c r="P24" s="18" t="n">
         <v>46343</v>
       </c>
-      <c r="P24" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O24,$J$8:$J$407)</f>
+      <c r="Q24" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P24,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23575,11 +23715,11 @@
         <f aca="false">IF($H25="","",$H25*$I25)</f>
         <v/>
       </c>
-      <c r="O25" s="18" t="n">
+      <c r="P25" s="18" t="n">
         <v>46344</v>
       </c>
-      <c r="P25" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O25,$J$8:$J$407)</f>
+      <c r="Q25" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P25,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23592,11 +23732,11 @@
         <f aca="false">IF($H26="","",$H26*$I26)</f>
         <v/>
       </c>
-      <c r="O26" s="18" t="n">
+      <c r="P26" s="18" t="n">
         <v>46345</v>
       </c>
-      <c r="P26" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O26,$J$8:$J$407)</f>
+      <c r="Q26" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P26,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23609,11 +23749,11 @@
         <f aca="false">IF($H27="","",$H27*$I27)</f>
         <v/>
       </c>
-      <c r="O27" s="18" t="n">
+      <c r="P27" s="18" t="n">
         <v>46346</v>
       </c>
-      <c r="P27" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O27,$J$8:$J$407)</f>
+      <c r="Q27" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P27,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23626,11 +23766,11 @@
         <f aca="false">IF($H28="","",$H28*$I28)</f>
         <v/>
       </c>
-      <c r="O28" s="18" t="n">
+      <c r="P28" s="18" t="n">
         <v>46347</v>
       </c>
-      <c r="P28" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O28,$J$8:$J$407)</f>
+      <c r="Q28" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P28,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23643,11 +23783,11 @@
         <f aca="false">IF($H29="","",$H29*$I29)</f>
         <v/>
       </c>
-      <c r="O29" s="18" t="n">
+      <c r="P29" s="18" t="n">
         <v>46348</v>
       </c>
-      <c r="P29" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O29,$J$8:$J$407)</f>
+      <c r="Q29" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P29,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23660,11 +23800,11 @@
         <f aca="false">IF($H30="","",$H30*$I30)</f>
         <v/>
       </c>
-      <c r="O30" s="18" t="n">
+      <c r="P30" s="18" t="n">
         <v>46349</v>
       </c>
-      <c r="P30" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O30,$J$8:$J$407)</f>
+      <c r="Q30" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P30,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23677,11 +23817,11 @@
         <f aca="false">IF($H31="","",$H31*$I31)</f>
         <v/>
       </c>
-      <c r="O31" s="18" t="n">
+      <c r="P31" s="18" t="n">
         <v>46350</v>
       </c>
-      <c r="P31" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O31,$J$8:$J$407)</f>
+      <c r="Q31" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P31,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23694,11 +23834,11 @@
         <f aca="false">IF($H32="","",$H32*$I32)</f>
         <v/>
       </c>
-      <c r="O32" s="18" t="n">
+      <c r="P32" s="18" t="n">
         <v>46351</v>
       </c>
-      <c r="P32" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O32,$J$8:$J$407)</f>
+      <c r="Q32" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P32,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23711,11 +23851,11 @@
         <f aca="false">IF($H33="","",$H33*$I33)</f>
         <v/>
       </c>
-      <c r="O33" s="18" t="n">
+      <c r="P33" s="18" t="n">
         <v>46352</v>
       </c>
-      <c r="P33" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O33,$J$8:$J$407)</f>
+      <c r="Q33" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P33,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23728,11 +23868,11 @@
         <f aca="false">IF($H34="","",$H34*$I34)</f>
         <v/>
       </c>
-      <c r="O34" s="18" t="n">
+      <c r="P34" s="18" t="n">
         <v>46353</v>
       </c>
-      <c r="P34" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O34,$J$8:$J$407)</f>
+      <c r="Q34" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P34,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23745,11 +23885,11 @@
         <f aca="false">IF($H35="","",$H35*$I35)</f>
         <v/>
       </c>
-      <c r="O35" s="18" t="n">
+      <c r="P35" s="18" t="n">
         <v>46354</v>
       </c>
-      <c r="P35" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O35,$J$8:$J$407)</f>
+      <c r="Q35" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P35,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23762,11 +23902,11 @@
         <f aca="false">IF($H36="","",$H36*$I36)</f>
         <v/>
       </c>
-      <c r="O36" s="18" t="n">
+      <c r="P36" s="18" t="n">
         <v>46355</v>
       </c>
-      <c r="P36" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O36,$J$8:$J$407)</f>
+      <c r="Q36" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P36,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23779,11 +23919,11 @@
         <f aca="false">IF($H37="","",$H37*$I37)</f>
         <v/>
       </c>
-      <c r="O37" s="18" t="n">
+      <c r="P37" s="18" t="n">
         <v>46356</v>
       </c>
-      <c r="P37" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O37,$J$8:$J$407)</f>
+      <c r="Q37" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P37,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -23796,11 +23936,11 @@
         <f aca="false">IF($H38="","",$H38*$I38)</f>
         <v/>
       </c>
-      <c r="O38" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P38" s="21" t="n">
-        <f aca="false">SUM($P$8:$P$37)</f>
+      <c r="P38" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q38" s="21" t="n">
+        <f aca="false">SUM($Q$8:$Q$37)</f>
         <v>0</v>
       </c>
     </row>
@@ -27496,11 +27636,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="P6:Q6"/>
   </mergeCells>
   <conditionalFormatting sqref="L8:L407">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -27531,7 +27671,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P407"/>
+  <dimension ref="A1:Q407"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="5"/>
@@ -27545,15 +27685,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="9" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -27567,10 +27708,11 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -27580,7 +27722,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -27590,7 +27732,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
@@ -27599,56 +27741,59 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O6" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" s="14" t="s">
         <v>44</v>
       </c>
+      <c r="N7" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="P7" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27660,11 +27805,11 @@
         <f aca="false">IF($H8="","",$H8*$I8)</f>
         <v/>
       </c>
-      <c r="O8" s="18" t="n">
+      <c r="P8" s="18" t="n">
         <v>46357</v>
       </c>
-      <c r="P8" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O8,$J$8:$J$407)</f>
+      <c r="Q8" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P8,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27677,11 +27822,11 @@
         <f aca="false">IF($H9="","",$H9*$I9)</f>
         <v/>
       </c>
-      <c r="O9" s="18" t="n">
+      <c r="P9" s="18" t="n">
         <v>46358</v>
       </c>
-      <c r="P9" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O9,$J$8:$J$407)</f>
+      <c r="Q9" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P9,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27694,11 +27839,11 @@
         <f aca="false">IF($H10="","",$H10*$I10)</f>
         <v/>
       </c>
-      <c r="O10" s="18" t="n">
+      <c r="P10" s="18" t="n">
         <v>46359</v>
       </c>
-      <c r="P10" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O10,$J$8:$J$407)</f>
+      <c r="Q10" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P10,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27711,11 +27856,11 @@
         <f aca="false">IF($H11="","",$H11*$I11)</f>
         <v/>
       </c>
-      <c r="O11" s="18" t="n">
+      <c r="P11" s="18" t="n">
         <v>46360</v>
       </c>
-      <c r="P11" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O11,$J$8:$J$407)</f>
+      <c r="Q11" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P11,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27728,11 +27873,11 @@
         <f aca="false">IF($H12="","",$H12*$I12)</f>
         <v/>
       </c>
-      <c r="O12" s="18" t="n">
+      <c r="P12" s="18" t="n">
         <v>46361</v>
       </c>
-      <c r="P12" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O12,$J$8:$J$407)</f>
+      <c r="Q12" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P12,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27745,11 +27890,11 @@
         <f aca="false">IF($H13="","",$H13*$I13)</f>
         <v/>
       </c>
-      <c r="O13" s="18" t="n">
+      <c r="P13" s="18" t="n">
         <v>46362</v>
       </c>
-      <c r="P13" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O13,$J$8:$J$407)</f>
+      <c r="Q13" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P13,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27762,11 +27907,11 @@
         <f aca="false">IF($H14="","",$H14*$I14)</f>
         <v/>
       </c>
-      <c r="O14" s="18" t="n">
+      <c r="P14" s="18" t="n">
         <v>46363</v>
       </c>
-      <c r="P14" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O14,$J$8:$J$407)</f>
+      <c r="Q14" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P14,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27779,11 +27924,11 @@
         <f aca="false">IF($H15="","",$H15*$I15)</f>
         <v/>
       </c>
-      <c r="O15" s="18" t="n">
+      <c r="P15" s="18" t="n">
         <v>46364</v>
       </c>
-      <c r="P15" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O15,$J$8:$J$407)</f>
+      <c r="Q15" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P15,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27796,11 +27941,11 @@
         <f aca="false">IF($H16="","",$H16*$I16)</f>
         <v/>
       </c>
-      <c r="O16" s="18" t="n">
+      <c r="P16" s="18" t="n">
         <v>46365</v>
       </c>
-      <c r="P16" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O16,$J$8:$J$407)</f>
+      <c r="Q16" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P16,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27813,11 +27958,11 @@
         <f aca="false">IF($H17="","",$H17*$I17)</f>
         <v/>
       </c>
-      <c r="O17" s="18" t="n">
+      <c r="P17" s="18" t="n">
         <v>46366</v>
       </c>
-      <c r="P17" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O17,$J$8:$J$407)</f>
+      <c r="Q17" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P17,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27830,11 +27975,11 @@
         <f aca="false">IF($H18="","",$H18*$I18)</f>
         <v/>
       </c>
-      <c r="O18" s="18" t="n">
+      <c r="P18" s="18" t="n">
         <v>46367</v>
       </c>
-      <c r="P18" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O18,$J$8:$J$407)</f>
+      <c r="Q18" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P18,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27847,11 +27992,11 @@
         <f aca="false">IF($H19="","",$H19*$I19)</f>
         <v/>
       </c>
-      <c r="O19" s="18" t="n">
+      <c r="P19" s="18" t="n">
         <v>46368</v>
       </c>
-      <c r="P19" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O19,$J$8:$J$407)</f>
+      <c r="Q19" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P19,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27864,11 +28009,11 @@
         <f aca="false">IF($H20="","",$H20*$I20)</f>
         <v/>
       </c>
-      <c r="O20" s="18" t="n">
+      <c r="P20" s="18" t="n">
         <v>46369</v>
       </c>
-      <c r="P20" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O20,$J$8:$J$407)</f>
+      <c r="Q20" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P20,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27881,11 +28026,11 @@
         <f aca="false">IF($H21="","",$H21*$I21)</f>
         <v/>
       </c>
-      <c r="O21" s="18" t="n">
+      <c r="P21" s="18" t="n">
         <v>46370</v>
       </c>
-      <c r="P21" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O21,$J$8:$J$407)</f>
+      <c r="Q21" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P21,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27898,11 +28043,11 @@
         <f aca="false">IF($H22="","",$H22*$I22)</f>
         <v/>
       </c>
-      <c r="O22" s="18" t="n">
+      <c r="P22" s="18" t="n">
         <v>46371</v>
       </c>
-      <c r="P22" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O22,$J$8:$J$407)</f>
+      <c r="Q22" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P22,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27915,11 +28060,11 @@
         <f aca="false">IF($H23="","",$H23*$I23)</f>
         <v/>
       </c>
-      <c r="O23" s="18" t="n">
+      <c r="P23" s="18" t="n">
         <v>46372</v>
       </c>
-      <c r="P23" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O23,$J$8:$J$407)</f>
+      <c r="Q23" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P23,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27932,11 +28077,11 @@
         <f aca="false">IF($H24="","",$H24*$I24)</f>
         <v/>
       </c>
-      <c r="O24" s="18" t="n">
+      <c r="P24" s="18" t="n">
         <v>46373</v>
       </c>
-      <c r="P24" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O24,$J$8:$J$407)</f>
+      <c r="Q24" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P24,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27949,11 +28094,11 @@
         <f aca="false">IF($H25="","",$H25*$I25)</f>
         <v/>
       </c>
-      <c r="O25" s="18" t="n">
+      <c r="P25" s="18" t="n">
         <v>46374</v>
       </c>
-      <c r="P25" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O25,$J$8:$J$407)</f>
+      <c r="Q25" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P25,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27966,11 +28111,11 @@
         <f aca="false">IF($H26="","",$H26*$I26)</f>
         <v/>
       </c>
-      <c r="O26" s="18" t="n">
+      <c r="P26" s="18" t="n">
         <v>46375</v>
       </c>
-      <c r="P26" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O26,$J$8:$J$407)</f>
+      <c r="Q26" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P26,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -27983,11 +28128,11 @@
         <f aca="false">IF($H27="","",$H27*$I27)</f>
         <v/>
       </c>
-      <c r="O27" s="18" t="n">
+      <c r="P27" s="18" t="n">
         <v>46376</v>
       </c>
-      <c r="P27" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O27,$J$8:$J$407)</f>
+      <c r="Q27" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P27,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28000,11 +28145,11 @@
         <f aca="false">IF($H28="","",$H28*$I28)</f>
         <v/>
       </c>
-      <c r="O28" s="18" t="n">
+      <c r="P28" s="18" t="n">
         <v>46377</v>
       </c>
-      <c r="P28" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O28,$J$8:$J$407)</f>
+      <c r="Q28" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P28,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28017,11 +28162,11 @@
         <f aca="false">IF($H29="","",$H29*$I29)</f>
         <v/>
       </c>
-      <c r="O29" s="18" t="n">
+      <c r="P29" s="18" t="n">
         <v>46378</v>
       </c>
-      <c r="P29" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O29,$J$8:$J$407)</f>
+      <c r="Q29" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P29,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28034,11 +28179,11 @@
         <f aca="false">IF($H30="","",$H30*$I30)</f>
         <v/>
       </c>
-      <c r="O30" s="18" t="n">
+      <c r="P30" s="18" t="n">
         <v>46379</v>
       </c>
-      <c r="P30" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O30,$J$8:$J$407)</f>
+      <c r="Q30" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P30,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28051,11 +28196,11 @@
         <f aca="false">IF($H31="","",$H31*$I31)</f>
         <v/>
       </c>
-      <c r="O31" s="18" t="n">
+      <c r="P31" s="18" t="n">
         <v>46380</v>
       </c>
-      <c r="P31" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O31,$J$8:$J$407)</f>
+      <c r="Q31" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P31,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28068,11 +28213,11 @@
         <f aca="false">IF($H32="","",$H32*$I32)</f>
         <v/>
       </c>
-      <c r="O32" s="18" t="n">
+      <c r="P32" s="18" t="n">
         <v>46381</v>
       </c>
-      <c r="P32" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O32,$J$8:$J$407)</f>
+      <c r="Q32" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P32,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28085,11 +28230,11 @@
         <f aca="false">IF($H33="","",$H33*$I33)</f>
         <v/>
       </c>
-      <c r="O33" s="18" t="n">
+      <c r="P33" s="18" t="n">
         <v>46382</v>
       </c>
-      <c r="P33" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O33,$J$8:$J$407)</f>
+      <c r="Q33" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P33,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28102,11 +28247,11 @@
         <f aca="false">IF($H34="","",$H34*$I34)</f>
         <v/>
       </c>
-      <c r="O34" s="18" t="n">
+      <c r="P34" s="18" t="n">
         <v>46383</v>
       </c>
-      <c r="P34" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O34,$J$8:$J$407)</f>
+      <c r="Q34" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P34,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28119,11 +28264,11 @@
         <f aca="false">IF($H35="","",$H35*$I35)</f>
         <v/>
       </c>
-      <c r="O35" s="18" t="n">
+      <c r="P35" s="18" t="n">
         <v>46384</v>
       </c>
-      <c r="P35" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O35,$J$8:$J$407)</f>
+      <c r="Q35" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P35,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28136,11 +28281,11 @@
         <f aca="false">IF($H36="","",$H36*$I36)</f>
         <v/>
       </c>
-      <c r="O36" s="18" t="n">
+      <c r="P36" s="18" t="n">
         <v>46385</v>
       </c>
-      <c r="P36" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O36,$J$8:$J$407)</f>
+      <c r="Q36" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P36,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28153,11 +28298,11 @@
         <f aca="false">IF($H37="","",$H37*$I37)</f>
         <v/>
       </c>
-      <c r="O37" s="18" t="n">
+      <c r="P37" s="18" t="n">
         <v>46386</v>
       </c>
-      <c r="P37" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O37,$J$8:$J$407)</f>
+      <c r="Q37" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P37,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28170,11 +28315,11 @@
         <f aca="false">IF($H38="","",$H38*$I38)</f>
         <v/>
       </c>
-      <c r="O38" s="18" t="n">
+      <c r="P38" s="18" t="n">
         <v>46387</v>
       </c>
-      <c r="P38" s="19" t="n">
-        <f aca="false">SUMIF($B$8:$B$407,$O38,$J$8:$J$407)</f>
+      <c r="Q38" s="19" t="n">
+        <f aca="false">SUMIF($B$8:$B$407,$P38,$J$8:$J$407)</f>
         <v>0</v>
       </c>
     </row>
@@ -28187,11 +28332,11 @@
         <f aca="false">IF($H39="","",$H39*$I39)</f>
         <v/>
       </c>
-      <c r="O39" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P39" s="21" t="n">
-        <f aca="false">SUM($P$8:$P$38)</f>
+      <c r="P39" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q39" s="21" t="n">
+        <f aca="false">SUM($Q$8:$Q$38)</f>
         <v>0</v>
       </c>
     </row>
@@ -31877,11 +32022,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="P6:Q6"/>
   </mergeCells>
   <conditionalFormatting sqref="L8:L407">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -31925,7 +32070,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -31938,7 +32083,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -31946,7 +32091,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B4" s="23"/>
       <c r="C4" s="24" t="n">
@@ -31959,19 +32104,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="B5" s="25"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
       <c r="F7" s="22" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
@@ -31979,33 +32124,33 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>46174</v>
@@ -32018,7 +32163,7 @@
         <v>8500000</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G9" s="27" t="n">
         <f aca="false">'Tháng 6'!$D$3</f>
@@ -32035,7 +32180,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>46181</v>
@@ -32048,24 +32193,24 @@
         <v>6000000</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="G10" s="27" t="n">
         <f aca="false">'Tháng 7'!$D$3</f>
-        <v>0</v>
+        <v>97000000</v>
       </c>
       <c r="H10" s="27" t="n">
         <f aca="false">'Tháng 7'!$D$4</f>
-        <v>0</v>
+        <v>50000000</v>
       </c>
       <c r="I10" s="27" t="n">
         <f aca="false">'Tháng 7'!$D$5</f>
-        <v>0</v>
+        <v>47000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>46188</v>
@@ -32078,7 +32223,7 @@
         <v>7000000</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G11" s="27" t="n">
         <f aca="false">'Tháng 8'!$D$3</f>
@@ -32095,7 +32240,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>46195</v>
@@ -32108,7 +32253,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="G12" s="27" t="n">
         <f aca="false">'Tháng 9'!$D$3</f>
@@ -32125,7 +32270,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>46202</v>
@@ -32138,7 +32283,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G13" s="27" t="n">
         <f aca="false">'Tháng 10'!$D$3</f>
@@ -32155,7 +32300,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>46209</v>
@@ -32168,7 +32313,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G14" s="27" t="n">
         <f aca="false">'Tháng 11'!$D$3</f>
@@ -32185,7 +32330,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B15" s="18" t="n">
         <v>46216</v>
@@ -32198,7 +32343,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="G15" s="27" t="n">
         <f aca="false">'Tháng 12'!$D$3</f>
@@ -32215,7 +32360,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>46223</v>
@@ -32225,12 +32370,12 @@
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">SUMIFS('Tháng 6'!$J$8:$J$407,'Tháng 6'!$B$8:$B$407,"&gt;="&amp;$B16,'Tháng 6'!$B$8:$B$407,"&lt;="&amp;$C16)+SUMIFS('Tháng 7'!$J$8:$J$407,'Tháng 7'!$B$8:$B$407,"&gt;="&amp;$B16,'Tháng 7'!$B$8:$B$407,"&lt;="&amp;$C16)+SUMIFS('Tháng 8'!$J$8:$J$407,'Tháng 8'!$B$8:$B$407,"&gt;="&amp;$B16,'Tháng 8'!$B$8:$B$407,"&lt;="&amp;$C16)+SUMIFS('Tháng 9'!$J$8:$J$407,'Tháng 9'!$B$8:$B$407,"&gt;="&amp;$B16,'Tháng 9'!$B$8:$B$407,"&lt;="&amp;$C16)+SUMIFS('Tháng 10'!$J$8:$J$407,'Tháng 10'!$B$8:$B$407,"&gt;="&amp;$B16,'Tháng 10'!$B$8:$B$407,"&lt;="&amp;$C16)+SUMIFS('Tháng 11'!$J$8:$J$407,'Tháng 11'!$B$8:$B$407,"&gt;="&amp;$B16,'Tháng 11'!$B$8:$B$407,"&lt;="&amp;$C16)+SUMIFS('Tháng 12'!$J$8:$J$407,'Tháng 12'!$B$8:$B$407,"&gt;="&amp;$B16,'Tháng 12'!$B$8:$B$407,"&lt;="&amp;$C16)</f>
-        <v>0</v>
+        <v>97000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B17" s="18" t="n">
         <v>46230</v>
@@ -32243,7 +32388,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
@@ -32251,7 +32396,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B18" s="18" t="n">
         <v>46237</v>
@@ -32264,7 +32409,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="G18" s="21" t="n">
         <f aca="false">SUM($G$9:$G$9)</f>
@@ -32281,7 +32426,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B19" s="18" t="n">
         <v>46244</v>
@@ -32294,24 +32439,24 @@
         <v>0</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="G19" s="21" t="n">
         <f aca="false">SUM($G$10:$G$12)</f>
-        <v>0</v>
+        <v>97000000</v>
       </c>
       <c r="H19" s="21" t="n">
         <f aca="false">SUM($H$10:$H$12)</f>
-        <v>0</v>
+        <v>50000000</v>
       </c>
       <c r="I19" s="21" t="n">
         <f aca="false">SUM($I$10:$I$12)</f>
-        <v>0</v>
+        <v>47000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B20" s="18" t="n">
         <v>46251</v>
@@ -32324,7 +32469,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="G20" s="21" t="n">
         <f aca="false">SUM($G$13:$G$15)</f>
@@ -32341,7 +32486,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>46258</v>
@@ -32356,7 +32501,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>46265</v>
@@ -32369,7 +32514,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
@@ -32377,7 +32522,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="B23" s="18" t="n">
         <v>46272</v>
@@ -32390,24 +32535,24 @@
         <v>0</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G23" s="29" t="n">
         <f aca="false">SUM($G$18:$G$20)</f>
-        <v>21500000</v>
+        <v>118500000</v>
       </c>
       <c r="H23" s="29" t="n">
         <f aca="false">SUM($H$18:$H$20)</f>
-        <v>15500000</v>
+        <v>65500000</v>
       </c>
       <c r="I23" s="29" t="n">
         <f aca="false">SUM($I$18:$I$20)</f>
-        <v>6000000</v>
+        <v>53000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>46279</v>
@@ -32422,7 +32567,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>46286</v>
@@ -32435,12 +32580,12 @@
         <v>0</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>46293</v>
@@ -32455,7 +32600,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B27" s="18" t="n">
         <v>46300</v>
@@ -32470,7 +32615,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>46307</v>
@@ -32485,7 +32630,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B29" s="18" t="n">
         <v>46314</v>
@@ -32500,7 +32645,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="B30" s="18" t="n">
         <v>46321</v>
@@ -32515,7 +32660,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="26" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B31" s="18" t="n">
         <v>46328</v>
@@ -32530,7 +32675,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="26" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="B32" s="18" t="n">
         <v>46335</v>
@@ -32545,7 +32690,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="B33" s="18" t="n">
         <v>46342</v>
@@ -32560,7 +32705,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="26" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B34" s="18" t="n">
         <v>46349</v>
@@ -32575,7 +32720,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B35" s="18" t="n">
         <v>46356</v>
@@ -32590,7 +32735,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B36" s="18" t="n">
         <v>46363</v>
@@ -32605,7 +32750,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="26" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B37" s="18" t="n">
         <v>46370</v>
@@ -32620,7 +32765,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="26" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B38" s="18" t="n">
         <v>46377</v>
@@ -32635,7 +32780,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="26" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B39" s="18" t="n">
         <v>46384</v>

--- a/bao-cao-doanh-thu/doanh thu thông tin đơn hàng.xlsx
+++ b/bao-cao-doanh-thu/doanh thu thông tin đơn hàng.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="158">
   <si>
     <t xml:space="preserve">HƯỚNG DẪN SỬ DỤNG FILE BÁO CÁO DOANH THU - THÔNG TIN ĐƠN HÀNG (THÁNG 6 - THÁNG 12/2026)</t>
   </si>
@@ -66,7 +66,10 @@
     <t xml:space="preserve">   • SỐ LƯỢNG và ĐƠN GIÁ chỉ gõ số (ví dụ 50 và 85000) — không gõ chữ 'cái', 'đ', dấu chấm phẩy.</t>
   </si>
   <si>
-    <t xml:space="preserve">   • TÌNH TRẠNG CHUYỂN KHOẢN: bấm vào ô sẽ có danh sách chọn 'Đã chuyển khoản' / 'Chưa chuyển khoản' (ô tự đổi màu xanh/đỏ).</t>
+    <t xml:space="preserve">   • TÌNH TRẠNG CHUYỂN KHOẢN: bấm vào ô sẽ có danh sách chọn 'Đã chuyển khoản' / 'Đã cọc' / 'Chưa chuyển khoản' (ô tự đổi màu XANH / VÀNG / ĐỎ).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • Khách đã cọc: chọn 'Đã cọc' — khi khách thanh toán đủ thì đổi lại thành 'Đã chuyển khoản'. Tổng tiền các đơn đã cọc hiện ở đầu sheet và trong BÁO CÁO NĂM.</t>
   </si>
   <si>
     <t xml:space="preserve">   • Sheet 'Tháng 6' có sẵn 3 dòng VÍ DỤ MẪU (chữ màu xanh dương) — hãy xóa hoặc ghi đè bằng dữ liệu thật của bạn.</t>
@@ -124,6 +127,9 @@
   </si>
   <si>
     <t xml:space="preserve">ĐÃ CHUYỂN KHOẢN (đ):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ĐÃ CỌC (đ):</t>
   </si>
   <si>
     <t xml:space="preserve">CHƯA CHUYỂN KHOẢN (đ):</t>
@@ -415,6 +421,9 @@
   </si>
   <si>
     <t xml:space="preserve">ĐÃ CK (đ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ĐÃ CỌC (đ)</t>
   </si>
   <si>
     <t xml:space="preserve">CHƯA CK (đ)</t>
@@ -897,11 +906,18 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -950,7 +966,7 @@
       <rgbColor rgb="FF00B0B0"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1157,7 +1173,7 @@
     <tabColor rgb="FF808080"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B37"/>
+  <dimension ref="B2:B38"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1238,15 +1254,15 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1256,15 +1272,15 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1274,15 +1290,15 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1297,15 +1313,15 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="B32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1315,16 +1331,21 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="3"/>
+      <c r="B35" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="B36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1367,7 +1388,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1385,7 +1406,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -1395,7 +1416,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -1405,31 +1426,39 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
+        <f aca="false">SUMIF($L$10:$L$335,"Đã cọc",$J$10:$J$335)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="n">
         <f aca="false">SUMIF($L$10:$L$335,"Chưa chuyển khoản",$J$10:$J$335)</f>
         <v>6000000</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="P6" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P7" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -1457,46 +1486,46 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P9" s="17" t="n">
         <v>46175</v>
@@ -1515,19 +1544,19 @@
         <v>46176</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H10" s="23" t="n">
         <v>100</v>
@@ -1540,16 +1569,16 @@
         <v>8500000</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M10" s="21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N10" s="21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P10" s="17" t="n">
         <v>46176</v>
@@ -2364,7 +2393,7 @@
       <c r="M38" s="27"/>
       <c r="N38" s="27"/>
       <c r="P38" s="31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q38" s="32" t="n">
         <f aca="false">SUM($Q$8:$Q$37)</f>
@@ -3495,7 +3524,7 @@
     </row>
     <row r="90" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B90" s="33"/>
       <c r="C90" s="33"/>
@@ -3516,46 +3545,46 @@
     </row>
     <row r="91" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G91" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M91" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N91" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3567,19 +3596,19 @@
         <v>46183</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E92" s="22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F92" s="22" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G92" s="21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H92" s="23" t="n">
         <v>50</v>
@@ -3592,16 +3621,16 @@
         <v>6000000</v>
       </c>
       <c r="K92" s="25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L92" s="21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M92" s="21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N92" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5344,7 +5373,7 @@
     </row>
     <row r="172" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -5365,46 +5394,46 @@
     </row>
     <row r="173" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E173" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F173" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G173" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H173" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I173" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J173" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K173" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L173" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N173" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5416,19 +5445,19 @@
         <v>46188</v>
       </c>
       <c r="C174" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D174" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E174" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F174" s="22" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G174" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H174" s="23" t="n">
         <v>200</v>
@@ -5441,16 +5470,16 @@
         <v>7000000</v>
       </c>
       <c r="K174" s="25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L174" s="21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M174" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N174" s="21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7193,7 +7222,7 @@
     </row>
     <row r="254" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B254" s="33"/>
       <c r="C254" s="33"/>
@@ -7214,46 +7243,46 @@
     </row>
     <row r="255" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B255" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E255" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F255" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G255" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H255" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I255" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J255" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K255" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L255" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N255" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9017,11 +9046,12 @@
       <c r="N335" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="K8:N8"/>
@@ -9037,12 +9067,15 @@
       <formula>"Đã chuyển khoản"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"Đã cọc"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"Chưa chuyển khoản"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản hoặc Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
-      <formula1>"Đã chuyển khoản,Chưa chuyển khoản"</formula1>
+    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản / Đã cọc / Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
+      <formula1>"Đã chuyển khoản,Đã cọc,Chưa chuyển khoản"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -9085,7 +9118,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -9103,7 +9136,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -9113,7 +9146,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -9123,31 +9156,39 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
+        <f aca="false">SUMIF($L$10:$L$335,"Đã cọc",$J$10:$J$335)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="n">
         <f aca="false">SUMIF($L$10:$L$335,"Chưa chuyển khoản",$J$10:$J$335)</f>
         <v>47000000</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="P6" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P7" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -9175,46 +9216,46 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P9" s="17" t="n">
         <v>46205</v>
@@ -10087,7 +10128,7 @@
       <c r="M39" s="27"/>
       <c r="N39" s="27"/>
       <c r="P39" s="31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q39" s="32" t="n">
         <f aca="false">SUM($Q$8:$Q$38)</f>
@@ -11196,7 +11237,7 @@
     </row>
     <row r="90" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="33" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B90" s="33"/>
       <c r="C90" s="33"/>
@@ -11217,46 +11258,46 @@
     </row>
     <row r="91" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G91" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M91" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N91" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13021,7 +13062,7 @@
     </row>
     <row r="172" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -13042,46 +13083,46 @@
     </row>
     <row r="173" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E173" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F173" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G173" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H173" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I173" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J173" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K173" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L173" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N173" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13093,19 +13134,19 @@
         <v>46224</v>
       </c>
       <c r="C174" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D174" s="21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E174" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F174" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G174" s="21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H174" s="23" t="n">
         <v>1000</v>
@@ -13119,11 +13160,11 @@
       </c>
       <c r="K174" s="27"/>
       <c r="L174" s="21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M174" s="27"/>
       <c r="N174" s="21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13135,17 +13176,17 @@
         <v>46224</v>
       </c>
       <c r="C175" s="21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D175" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E175" s="28"/>
       <c r="F175" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G175" s="21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H175" s="23" t="n">
         <v>1000</v>
@@ -13159,7 +13200,7 @@
       </c>
       <c r="K175" s="27"/>
       <c r="L175" s="21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M175" s="27"/>
       <c r="N175" s="27"/>
@@ -14882,7 +14923,7 @@
     </row>
     <row r="254" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="33" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B254" s="33"/>
       <c r="C254" s="33"/>
@@ -14903,46 +14944,46 @@
     </row>
     <row r="255" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B255" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E255" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F255" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G255" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H255" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I255" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J255" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K255" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L255" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N255" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16706,11 +16747,12 @@
       <c r="N335" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="K8:N8"/>
@@ -16726,12 +16768,15 @@
       <formula>"Đã chuyển khoản"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"Đã cọc"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"Chưa chuyển khoản"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản hoặc Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
-      <formula1>"Đã chuyển khoản,Chưa chuyển khoản"</formula1>
+    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản / Đã cọc / Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
+      <formula1>"Đã chuyển khoản,Đã cọc,Chưa chuyển khoản"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -16774,7 +16819,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -16792,7 +16837,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -16802,7 +16847,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -16812,31 +16857,39 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
+        <f aca="false">SUMIF($L$10:$L$335,"Đã cọc",$J$10:$J$335)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="n">
         <f aca="false">SUMIF($L$10:$L$335,"Chưa chuyển khoản",$J$10:$J$335)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="P6" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P7" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -16864,46 +16917,46 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P9" s="17" t="n">
         <v>46236</v>
@@ -17776,7 +17829,7 @@
       <c r="M39" s="27"/>
       <c r="N39" s="27"/>
       <c r="P39" s="31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q39" s="32" t="n">
         <f aca="false">SUM($Q$8:$Q$38)</f>
@@ -18885,7 +18938,7 @@
     </row>
     <row r="90" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B90" s="33"/>
       <c r="C90" s="33"/>
@@ -18906,46 +18959,46 @@
     </row>
     <row r="91" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G91" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M91" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N91" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20710,7 +20763,7 @@
     </row>
     <row r="172" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -20731,46 +20784,46 @@
     </row>
     <row r="173" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E173" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F173" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G173" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H173" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I173" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J173" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K173" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L173" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N173" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22535,7 +22588,7 @@
     </row>
     <row r="254" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B254" s="33"/>
       <c r="C254" s="33"/>
@@ -22556,46 +22609,46 @@
     </row>
     <row r="255" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B255" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E255" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F255" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G255" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H255" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I255" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J255" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K255" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L255" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N255" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24359,11 +24412,12 @@
       <c r="N335" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="K8:N8"/>
@@ -24379,12 +24433,15 @@
       <formula>"Đã chuyển khoản"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"Đã cọc"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"Chưa chuyển khoản"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản hoặc Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
-      <formula1>"Đã chuyển khoản,Chưa chuyển khoản"</formula1>
+    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản / Đã cọc / Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
+      <formula1>"Đã chuyển khoản,Đã cọc,Chưa chuyển khoản"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -24427,7 +24484,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -24445,7 +24502,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -24455,7 +24512,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -24465,31 +24522,39 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
+        <f aca="false">SUMIF($L$10:$L$335,"Đã cọc",$J$10:$J$335)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="n">
         <f aca="false">SUMIF($L$10:$L$335,"Chưa chuyển khoản",$J$10:$J$335)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="P6" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P7" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -24517,46 +24582,46 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P9" s="17" t="n">
         <v>46267</v>
@@ -25400,7 +25465,7 @@
       <c r="M38" s="27"/>
       <c r="N38" s="27"/>
       <c r="P38" s="31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q38" s="32" t="n">
         <f aca="false">SUM($Q$8:$Q$37)</f>
@@ -26531,7 +26596,7 @@
     </row>
     <row r="90" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B90" s="33"/>
       <c r="C90" s="33"/>
@@ -26552,46 +26617,46 @@
     </row>
     <row r="91" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G91" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M91" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N91" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28356,7 +28421,7 @@
     </row>
     <row r="172" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -28377,46 +28442,46 @@
     </row>
     <row r="173" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E173" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F173" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G173" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H173" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I173" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J173" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K173" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L173" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N173" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30181,7 +30246,7 @@
     </row>
     <row r="254" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B254" s="33"/>
       <c r="C254" s="33"/>
@@ -30202,46 +30267,46 @@
     </row>
     <row r="255" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B255" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E255" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F255" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G255" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H255" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I255" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J255" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K255" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L255" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N255" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32005,11 +32070,12 @@
       <c r="N335" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="K8:N8"/>
@@ -32025,12 +32091,15 @@
       <formula>"Đã chuyển khoản"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"Đã cọc"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"Chưa chuyển khoản"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản hoặc Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
-      <formula1>"Đã chuyển khoản,Chưa chuyển khoản"</formula1>
+    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản / Đã cọc / Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
+      <formula1>"Đã chuyển khoản,Đã cọc,Chưa chuyển khoản"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -32073,7 +32142,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -32091,7 +32160,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -32101,7 +32170,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -32111,31 +32180,39 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
+        <f aca="false">SUMIF($L$10:$L$335,"Đã cọc",$J$10:$J$335)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="n">
         <f aca="false">SUMIF($L$10:$L$335,"Chưa chuyển khoản",$J$10:$J$335)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="P6" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P7" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -32163,46 +32240,46 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P9" s="17" t="n">
         <v>46297</v>
@@ -33075,7 +33152,7 @@
       <c r="M39" s="27"/>
       <c r="N39" s="27"/>
       <c r="P39" s="31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q39" s="32" t="n">
         <f aca="false">SUM($Q$8:$Q$38)</f>
@@ -34184,7 +34261,7 @@
     </row>
     <row r="90" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B90" s="33"/>
       <c r="C90" s="33"/>
@@ -34205,46 +34282,46 @@
     </row>
     <row r="91" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G91" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M91" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N91" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36009,7 +36086,7 @@
     </row>
     <row r="172" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -36030,46 +36107,46 @@
     </row>
     <row r="173" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E173" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F173" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G173" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H173" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I173" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J173" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K173" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L173" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N173" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37834,7 +37911,7 @@
     </row>
     <row r="254" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B254" s="33"/>
       <c r="C254" s="33"/>
@@ -37855,46 +37932,46 @@
     </row>
     <row r="255" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B255" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E255" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F255" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G255" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H255" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I255" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J255" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K255" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L255" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N255" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39658,11 +39735,12 @@
       <c r="N335" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="K8:N8"/>
@@ -39678,12 +39756,15 @@
       <formula>"Đã chuyển khoản"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"Đã cọc"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"Chưa chuyển khoản"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản hoặc Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
-      <formula1>"Đã chuyển khoản,Chưa chuyển khoản"</formula1>
+    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản / Đã cọc / Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
+      <formula1>"Đã chuyển khoản,Đã cọc,Chưa chuyển khoản"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -39726,7 +39807,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -39744,7 +39825,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -39754,7 +39835,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -39764,31 +39845,39 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
+        <f aca="false">SUMIF($L$10:$L$335,"Đã cọc",$J$10:$J$335)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="n">
         <f aca="false">SUMIF($L$10:$L$335,"Chưa chuyển khoản",$J$10:$J$335)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="P6" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P7" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -39816,46 +39905,46 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P9" s="17" t="n">
         <v>46328</v>
@@ -40699,7 +40788,7 @@
       <c r="M38" s="27"/>
       <c r="N38" s="27"/>
       <c r="P38" s="31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q38" s="32" t="n">
         <f aca="false">SUM($Q$8:$Q$37)</f>
@@ -41830,7 +41919,7 @@
     </row>
     <row r="90" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B90" s="33"/>
       <c r="C90" s="33"/>
@@ -41851,46 +41940,46 @@
     </row>
     <row r="91" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G91" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M91" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N91" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43655,7 +43744,7 @@
     </row>
     <row r="172" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -43676,46 +43765,46 @@
     </row>
     <row r="173" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E173" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F173" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G173" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H173" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I173" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J173" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K173" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L173" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N173" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45480,7 +45569,7 @@
     </row>
     <row r="254" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B254" s="33"/>
       <c r="C254" s="33"/>
@@ -45501,46 +45590,46 @@
     </row>
     <row r="255" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B255" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E255" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F255" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G255" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H255" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I255" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J255" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K255" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L255" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N255" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47304,11 +47393,12 @@
       <c r="N335" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="K8:N8"/>
@@ -47324,12 +47414,15 @@
       <formula>"Đã chuyển khoản"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"Đã cọc"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"Chưa chuyển khoản"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản hoặc Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
-      <formula1>"Đã chuyển khoản,Chưa chuyển khoản"</formula1>
+    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản / Đã cọc / Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
+      <formula1>"Đã chuyển khoản,Đã cọc,Chưa chuyển khoản"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -47372,7 +47465,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -47390,7 +47483,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="n">
@@ -47400,7 +47493,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="12" t="n">
@@ -47410,31 +47503,39 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12" t="n">
+        <f aca="false">SUMIF($L$10:$L$335,"Đã cọc",$J$10:$J$335)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="n">
         <f aca="false">SUMIF($L$10:$L$335,"Chưa chuyển khoản",$J$10:$J$335)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="P6" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P7" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -47462,46 +47563,46 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P9" s="17" t="n">
         <v>46358</v>
@@ -48374,7 +48475,7 @@
       <c r="M39" s="27"/>
       <c r="N39" s="27"/>
       <c r="P39" s="31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q39" s="32" t="n">
         <f aca="false">SUM($Q$8:$Q$38)</f>
@@ -49483,7 +49584,7 @@
     </row>
     <row r="90" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B90" s="33"/>
       <c r="C90" s="33"/>
@@ -49504,46 +49605,46 @@
     </row>
     <row r="91" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G91" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M91" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N91" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51308,7 +51409,7 @@
     </row>
     <row r="172" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -51329,46 +51430,46 @@
     </row>
     <row r="173" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E173" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F173" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G173" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H173" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I173" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J173" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K173" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L173" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M173" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N173" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53133,7 +53234,7 @@
     </row>
     <row r="254" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B254" s="33"/>
       <c r="C254" s="33"/>
@@ -53154,46 +53255,46 @@
     </row>
     <row r="255" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B255" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E255" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F255" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G255" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H255" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I255" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J255" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K255" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L255" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M255" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N255" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54957,11 +55058,12 @@
       <c r="N335" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="K8:N8"/>
@@ -54977,12 +55079,15 @@
       <formula>"Đã chuyển khoản"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"Đã cọc"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"Chưa chuyển khoản"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản hoặc Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
-      <formula1>"Đã chuyển khoản,Chưa chuyển khoản"</formula1>
+    <dataValidation allowBlank="true" error="Chọn: Đã chuyển khoản / Đã cọc / Chưa chuyển khoản" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L10:L89 L92:L171 L174:L253 L256:L335" type="list">
+      <formula1>"Đã chuyển khoản,Đã cọc,Chưa chuyển khoản"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -55002,7 +55107,7 @@
     <tabColor rgb="FF1F4E78"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -55010,12 +55115,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -55028,7 +55134,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="35" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B3" s="35"/>
       <c r="C3" s="35"/>
@@ -55036,7 +55142,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B4" s="36"/>
       <c r="C4" s="37" t="n">
@@ -55049,60 +55155,64 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B5" s="38"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B7" s="35"/>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
       <c r="E7" s="35"/>
       <c r="F7" s="35" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G7" s="35"/>
       <c r="H7" s="35"/>
       <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>124</v>
-      </c>
       <c r="G8" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>129</v>
+        <v>131</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C9" s="40" t="n">
         <v>46174</v>
@@ -55115,7 +55225,7 @@
         <v>8500000</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G9" s="43" t="n">
         <f aca="false">'Tháng 6'!$D$3</f>
@@ -55127,15 +55237,19 @@
       </c>
       <c r="I9" s="43" t="n">
         <f aca="false">'Tháng 6'!$D$5</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="43" t="n">
+        <f aca="false">'Tháng 6'!$D$6</f>
         <v>6000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="39" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C10" s="40" t="n">
         <v>46181</v>
@@ -55148,7 +55262,7 @@
         <v>6000000</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G10" s="43" t="n">
         <f aca="false">'Tháng 7'!$D$3</f>
@@ -55160,15 +55274,19 @@
       </c>
       <c r="I10" s="43" t="n">
         <f aca="false">'Tháng 7'!$D$5</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="43" t="n">
+        <f aca="false">'Tháng 7'!$D$6</f>
         <v>47000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C11" s="40" t="n">
         <v>46188</v>
@@ -55181,7 +55299,7 @@
         <v>7000000</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G11" s="43" t="n">
         <f aca="false">'Tháng 8'!$D$3</f>
@@ -55195,13 +55313,17 @@
         <f aca="false">'Tháng 8'!$D$5</f>
         <v>0</v>
       </c>
+      <c r="J11" s="43" t="n">
+        <f aca="false">'Tháng 8'!$D$6</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="39" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C12" s="40" t="n">
         <v>46195</v>
@@ -55214,7 +55336,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G12" s="43" t="n">
         <f aca="false">'Tháng 9'!$D$3</f>
@@ -55228,13 +55350,17 @@
         <f aca="false">'Tháng 9'!$D$5</f>
         <v>0</v>
       </c>
+      <c r="J12" s="43" t="n">
+        <f aca="false">'Tháng 9'!$D$6</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="42" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C13" s="17" t="n">
         <v>46204</v>
@@ -55247,7 +55373,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G13" s="43" t="n">
         <f aca="false">'Tháng 10'!$D$3</f>
@@ -55261,13 +55387,17 @@
         <f aca="false">'Tháng 10'!$D$5</f>
         <v>0</v>
       </c>
+      <c r="J13" s="43" t="n">
+        <f aca="false">'Tháng 10'!$D$6</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="42" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C14" s="17" t="n">
         <v>46211</v>
@@ -55280,7 +55410,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G14" s="43" t="n">
         <f aca="false">'Tháng 11'!$D$3</f>
@@ -55294,13 +55424,17 @@
         <f aca="false">'Tháng 11'!$D$5</f>
         <v>0</v>
       </c>
+      <c r="J14" s="43" t="n">
+        <f aca="false">'Tháng 11'!$D$6</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="42" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C15" s="17" t="n">
         <v>46218</v>
@@ -55313,7 +55447,7 @@
         <v>97000000</v>
       </c>
       <c r="F15" s="42" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G15" s="43" t="n">
         <f aca="false">'Tháng 12'!$D$3</f>
@@ -55327,13 +55461,17 @@
         <f aca="false">'Tháng 12'!$D$5</f>
         <v>0</v>
       </c>
+      <c r="J15" s="43" t="n">
+        <f aca="false">'Tháng 12'!$D$6</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="42" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C16" s="17" t="n">
         <v>46225</v>
@@ -55348,10 +55486,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="39" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C17" s="40" t="n">
         <v>46235</v>
@@ -55364,18 +55502,19 @@
         <v>0</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
       <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C18" s="40" t="n">
         <v>46242</v>
@@ -55388,7 +55527,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G18" s="32" t="n">
         <f aca="false">SUM($G$9:$G$9)</f>
@@ -55400,15 +55539,19 @@
       </c>
       <c r="I18" s="32" t="n">
         <f aca="false">SUM($I$9:$I$9)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="32" t="n">
+        <f aca="false">SUM($J$9:$J$9)</f>
         <v>6000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C19" s="40" t="n">
         <v>46249</v>
@@ -55421,7 +55564,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G19" s="32" t="n">
         <f aca="false">SUM($G$10:$G$12)</f>
@@ -55433,15 +55576,19 @@
       </c>
       <c r="I19" s="32" t="n">
         <f aca="false">SUM($I$10:$I$12)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="32" t="n">
+        <f aca="false">SUM($J$10:$J$12)</f>
         <v>47000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C20" s="40" t="n">
         <v>46256</v>
@@ -55454,7 +55601,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G20" s="32" t="n">
         <f aca="false">SUM($G$13:$G$15)</f>
@@ -55468,13 +55615,17 @@
         <f aca="false">SUM($I$13:$I$15)</f>
         <v>0</v>
       </c>
+      <c r="J20" s="32" t="n">
+        <f aca="false">SUM($J$13:$J$15)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C21" s="17" t="n">
         <v>46266</v>
@@ -55489,10 +55640,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C22" s="17" t="n">
         <v>46273</v>
@@ -55505,18 +55656,19 @@
         <v>0</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G22" s="35"/>
       <c r="H22" s="35"/>
       <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C23" s="17" t="n">
         <v>46280</v>
@@ -55529,7 +55681,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G23" s="45" t="n">
         <f aca="false">SUM($G$18:$G$20)</f>
@@ -55541,15 +55693,19 @@
       </c>
       <c r="I23" s="45" t="n">
         <f aca="false">SUM($I$18:$I$20)</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="45" t="n">
+        <f aca="false">SUM($J$18:$J$20)</f>
         <v>53000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C24" s="17" t="n">
         <v>46287</v>
@@ -55564,10 +55720,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="39" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C25" s="40" t="n">
         <v>46296</v>
@@ -55580,15 +55736,15 @@
         <v>0</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="39" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C26" s="40" t="n">
         <v>46303</v>
@@ -55603,10 +55759,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="39" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C27" s="40" t="n">
         <v>46310</v>
@@ -55621,10 +55777,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="39" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C28" s="40" t="n">
         <v>46317</v>
@@ -55639,10 +55795,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="42" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C29" s="17" t="n">
         <v>46327</v>
@@ -55657,10 +55813,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="42" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C30" s="17" t="n">
         <v>46334</v>
@@ -55675,10 +55831,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="42" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C31" s="17" t="n">
         <v>46341</v>
@@ -55693,10 +55849,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="42" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B32" s="42" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C32" s="17" t="n">
         <v>46348</v>
@@ -55711,10 +55867,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="39" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C33" s="40" t="n">
         <v>46357</v>
@@ -55729,10 +55885,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="39" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C34" s="40" t="n">
         <v>46364</v>
@@ -55747,10 +55903,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="39" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C35" s="40" t="n">
         <v>46371</v>
@@ -55765,10 +55921,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="39" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C36" s="40" t="n">
         <v>46378</v>
@@ -55788,9 +55944,9 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="F22:J22"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
